--- a/data/processed/interpolated_data.xlsx
+++ b/data/processed/interpolated_data.xlsx
@@ -463,7 +463,7 @@
         <v>0.125</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1993825447932754</v>
+        <v>0.2067495718606536</v>
       </c>
     </row>
     <row r="4">
@@ -477,7 +477,7 @@
         <v>0.15</v>
       </c>
       <c r="D4" t="n">
-        <v>0.2262841608897189</v>
+        <v>0.235750272507586</v>
       </c>
     </row>
     <row r="5">
@@ -491,7 +491,7 @@
         <v>0.175</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2531857769861623</v>
+        <v>0.2600179173455849</v>
       </c>
     </row>
     <row r="6">
@@ -519,7 +519,7 @@
         <v>0.225</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2923358796069598</v>
+        <v>0.2964935864266043</v>
       </c>
     </row>
     <row r="8">
@@ -533,7 +533,7 @@
         <v>0.25</v>
       </c>
       <c r="D8" t="n">
-        <v>0.3045843661313138</v>
+        <v>0.3097713840855361</v>
       </c>
     </row>
     <row r="9">
@@ -547,7 +547,7 @@
         <v>0.275</v>
       </c>
       <c r="D9" t="n">
-        <v>0.3168328526556677</v>
+        <v>0.3204556727673567</v>
       </c>
     </row>
     <row r="10">
@@ -575,7 +575,7 @@
         <v>0.325</v>
       </c>
       <c r="D11" t="n">
-        <v>0.3349959787869885</v>
+        <v>0.3361683384894501</v>
       </c>
     </row>
     <row r="12">
@@ -589,7 +589,7 @@
         <v>0.35</v>
       </c>
       <c r="D12" t="n">
-        <v>0.3409106183939553</v>
+        <v>0.3421768996934139</v>
       </c>
     </row>
     <row r="13">
@@ -603,7 +603,7 @@
         <v>0.375</v>
       </c>
       <c r="D13" t="n">
-        <v>0.3468252580009221</v>
+        <v>0.3475523202476483</v>
       </c>
     </row>
     <row r="14">
@@ -631,7 +631,7 @@
         <v>0.4249999999999999</v>
       </c>
       <c r="D15" t="n">
-        <v>0.3555221021822784</v>
+        <v>0.3579247884748993</v>
       </c>
     </row>
     <row r="16">
@@ -645,7 +645,7 @@
         <v>0.45</v>
       </c>
       <c r="D16" t="n">
-        <v>0.3583043067566678</v>
+        <v>0.362251586529558</v>
       </c>
     </row>
     <row r="17">
@@ -659,7 +659,7 @@
         <v>0.475</v>
       </c>
       <c r="D17" t="n">
-        <v>0.3610865113310573</v>
+        <v>0.3646047446977715</v>
       </c>
     </row>
     <row r="18">
@@ -687,7 +687,7 @@
         <v>0.525</v>
       </c>
       <c r="D19" t="n">
-        <v>0.3583795899392689</v>
+        <v>0.3594621784283629</v>
       </c>
     </row>
     <row r="20">
@@ -701,7 +701,7 @@
         <v>0.5499999999999999</v>
       </c>
       <c r="D20" t="n">
-        <v>0.3528904639730912</v>
+        <v>0.3529407119417888</v>
       </c>
     </row>
     <row r="21">
@@ -715,7 +715,7 @@
         <v>0.575</v>
       </c>
       <c r="D21" t="n">
-        <v>0.3474013380069133</v>
+        <v>0.3463941214708658</v>
       </c>
     </row>
     <row r="22">
@@ -743,7 +743,7 @@
         <v>0.6249999999999999</v>
       </c>
       <c r="D23" t="n">
-        <v>0.3530410303382933</v>
+        <v>0.3415847886765391</v>
       </c>
     </row>
     <row r="24">
@@ -757,7 +757,7 @@
         <v>0.6499999999999999</v>
       </c>
       <c r="D24" t="n">
-        <v>0.3641698486358512</v>
+        <v>0.3475016564034179</v>
       </c>
     </row>
     <row r="25">
@@ -771,7 +771,7 @@
         <v>0.6749999999999999</v>
       </c>
       <c r="D25" t="n">
-        <v>0.3752986669334091</v>
+        <v>0.3617526202465134</v>
       </c>
     </row>
     <row r="26">
@@ -813,7 +813,7 @@
         <v>0.125</v>
       </c>
       <c r="D28" t="n">
-        <v>0.3312089073839666</v>
+        <v>0.3436900825309346</v>
       </c>
     </row>
     <row r="29">
@@ -827,7 +827,7 @@
         <v>0.15</v>
       </c>
       <c r="D29" t="n">
-        <v>0.3669411426040666</v>
+        <v>0.3826567651247872</v>
       </c>
     </row>
     <row r="30">
@@ -841,7 +841,7 @@
         <v>0.175</v>
       </c>
       <c r="D30" t="n">
-        <v>0.4026733778241667</v>
+        <v>0.4137656364582796</v>
       </c>
     </row>
     <row r="31">
@@ -869,7 +869,7 @@
         <v>0.225</v>
       </c>
       <c r="D32" t="n">
-        <v>0.4538179353257671</v>
+        <v>0.4579656113956041</v>
       </c>
     </row>
     <row r="33">
@@ -883,7 +883,7 @@
         <v>0.25</v>
       </c>
       <c r="D33" t="n">
-        <v>0.4692302576072674</v>
+        <v>0.4738345480251466</v>
       </c>
     </row>
     <row r="34">
@@ -897,7 +897,7 @@
         <v>0.275</v>
       </c>
       <c r="D34" t="n">
-        <v>0.4846425798887677</v>
+        <v>0.4874013394457495</v>
       </c>
     </row>
     <row r="35">
@@ -925,7 +925,7 @@
         <v>0.325</v>
       </c>
       <c r="D36" t="n">
-        <v>0.5092940034784758</v>
+        <v>0.5126794044465336</v>
       </c>
     </row>
     <row r="37">
@@ -939,7 +939,7 @@
         <v>0.35</v>
       </c>
       <c r="D37" t="n">
-        <v>0.5185331047866837</v>
+        <v>0.5241400214622847</v>
       </c>
     </row>
     <row r="38">
@@ -953,7 +953,7 @@
         <v>0.375</v>
       </c>
       <c r="D38" t="n">
-        <v>0.5277722060948915</v>
+        <v>0.532797180140235</v>
       </c>
     </row>
     <row r="39">
@@ -981,7 +981,7 @@
         <v>0.4249999999999999</v>
       </c>
       <c r="D40" t="n">
-        <v>0.5318091303792999</v>
+        <v>0.5357609014009347</v>
       </c>
     </row>
     <row r="41">
@@ -995,7 +995,7 @@
         <v>0.45</v>
       </c>
       <c r="D41" t="n">
-        <v>0.5266069533555002</v>
+        <v>0.5304967451931673</v>
       </c>
     </row>
     <row r="42">
@@ -1009,7 +1009,7 @@
         <v>0.475</v>
       </c>
       <c r="D42" t="n">
-        <v>0.5214047763317007</v>
+        <v>0.5232876930665664</v>
       </c>
     </row>
     <row r="43">
@@ -1037,7 +1037,7 @@
         <v>0.525</v>
       </c>
       <c r="D44" t="n">
-        <v>0.5143063359548465</v>
+        <v>0.5109687346446857</v>
       </c>
     </row>
     <row r="45">
@@ -1051,7 +1051,7 @@
         <v>0.5499999999999999</v>
       </c>
       <c r="D45" t="n">
-        <v>0.5124100726017921</v>
+        <v>0.5079470355674165</v>
       </c>
     </row>
     <row r="46">
@@ -1065,7 +1065,7 @@
         <v>0.575</v>
       </c>
       <c r="D46" t="n">
-        <v>0.5105138092487376</v>
+        <v>0.5071568550073351</v>
       </c>
     </row>
     <row r="47">
@@ -1093,7 +1093,7 @@
         <v>0.6249999999999999</v>
       </c>
       <c r="D48" t="n">
-        <v>0.5158021800613124</v>
+        <v>0.5123484611637019</v>
       </c>
     </row>
     <row r="49">
@@ -1107,7 +1107,7 @@
         <v>0.6499999999999999</v>
       </c>
       <c r="D49" t="n">
-        <v>0.5229868142269416</v>
+        <v>0.5183689537426334</v>
       </c>
     </row>
     <row r="50">
@@ -1121,7 +1121,7 @@
         <v>0.6749999999999999</v>
       </c>
       <c r="D50" t="n">
-        <v>0.5301714483925709</v>
+        <v>0.5266983765637189</v>
       </c>
     </row>
     <row r="51">
@@ -1135,7 +1135,7 @@
         <v>0.7</v>
       </c>
       <c r="D51" t="n">
-        <v>0.5373560825582002</v>
+        <v>0.5373560825582003</v>
       </c>
     </row>
     <row r="52">
@@ -1163,7 +1163,7 @@
         <v>0.125</v>
       </c>
       <c r="D53" t="n">
-        <v>0.4549677168256036</v>
+        <v>0.4687693177822853</v>
       </c>
     </row>
     <row r="54">
@@ -1177,7 +1177,7 @@
         <v>0.15</v>
       </c>
       <c r="D54" t="n">
-        <v>0.5036834206443681</v>
+        <v>0.5215644684935141</v>
       </c>
     </row>
     <row r="55">
@@ -1191,7 +1191,7 @@
         <v>0.175</v>
       </c>
       <c r="D55" t="n">
-        <v>0.5523991244631327</v>
+        <v>0.5654190952801699</v>
       </c>
     </row>
     <row r="56">
@@ -1219,7 +1219,7 @@
         <v>0.225</v>
       </c>
       <c r="D57" t="n">
-        <v>0.6203214775195252</v>
+        <v>0.6294332976383402</v>
       </c>
     </row>
     <row r="58">
@@ -1233,7 +1233,7 @@
         <v>0.25</v>
       </c>
       <c r="D58" t="n">
-        <v>0.6395281267571531</v>
+        <v>0.6511561334891438</v>
       </c>
     </row>
     <row r="59">
@@ -1247,7 +1247,7 @@
         <v>0.275</v>
       </c>
       <c r="D59" t="n">
-        <v>0.6587347759947811</v>
+        <v>0.6670649659739517</v>
       </c>
     </row>
     <row r="60">
@@ -1275,7 +1275,7 @@
         <v>0.325</v>
       </c>
       <c r="D61" t="n">
-        <v>0.6846297468337857</v>
+        <v>0.6848474316985709</v>
       </c>
     </row>
     <row r="62">
@@ -1289,7 +1289,7 @@
         <v>0.35</v>
       </c>
       <c r="D62" t="n">
-        <v>0.6913180684351625</v>
+        <v>0.6899660669841361</v>
       </c>
     </row>
     <row r="63">
@@ -1303,7 +1303,7 @@
         <v>0.375</v>
       </c>
       <c r="D63" t="n">
-        <v>0.6980063900365392</v>
+        <v>0.6957607029952145</v>
       </c>
     </row>
     <row r="64">
@@ -1331,7 +1331,7 @@
         <v>0.4249999999999999</v>
       </c>
       <c r="D65" t="n">
-        <v>0.7170755656363738</v>
+        <v>0.7181865619587344</v>
       </c>
     </row>
     <row r="66">
@@ -1345,7 +1345,7 @@
         <v>0.45</v>
       </c>
       <c r="D66" t="n">
-        <v>0.7294564196348315</v>
+        <v>0.733475111565702</v>
       </c>
     </row>
     <row r="67">
@@ -1359,7 +1359,7 @@
         <v>0.475</v>
       </c>
       <c r="D67" t="n">
-        <v>0.7418372736332894</v>
+        <v>0.7467543152072342</v>
       </c>
     </row>
     <row r="68">
@@ -1387,7 +1387,7 @@
         <v>0.525</v>
       </c>
       <c r="D69" t="n">
-        <v>0.7458758126874114</v>
+        <v>0.7531706646458832</v>
       </c>
     </row>
     <row r="70">
@@ -1401,7 +1401,7 @@
         <v>0.5499999999999999</v>
       </c>
       <c r="D70" t="n">
-        <v>0.7375334977430756</v>
+        <v>0.7453566862891893</v>
       </c>
     </row>
     <row r="71">
@@ -1415,7 +1415,7 @@
         <v>0.575</v>
       </c>
       <c r="D71" t="n">
-        <v>0.7291911827987398</v>
+        <v>0.7336311136594383</v>
       </c>
     </row>
     <row r="72">
@@ -1443,7 +1443,7 @@
         <v>0.6249999999999999</v>
       </c>
       <c r="D73" t="n">
-        <v>0.7196995446000268</v>
+        <v>0.7098648699718594</v>
       </c>
     </row>
     <row r="74">
@@ -1457,7 +1457,7 @@
         <v>0.6499999999999999</v>
       </c>
       <c r="D74" t="n">
-        <v>0.7185502213456496</v>
+        <v>0.7035340411095774</v>
       </c>
     </row>
     <row r="75">
@@ -1471,7 +1471,7 @@
         <v>0.6749999999999999</v>
       </c>
       <c r="D75" t="n">
-        <v>0.7174008980912724</v>
+        <v>0.7047113023653317</v>
       </c>
     </row>
     <row r="76">
@@ -1513,7 +1513,7 @@
         <v>0.125</v>
       </c>
       <c r="D78" t="n">
-        <v>0.5028099720671025</v>
+        <v>0.5216146376221229</v>
       </c>
     </row>
     <row r="79">
@@ -1527,7 +1527,7 @@
         <v>0.15</v>
       </c>
       <c r="D79" t="n">
-        <v>0.5561547296779485</v>
+        <v>0.580220025226584</v>
       </c>
     </row>
     <row r="80">
@@ -1541,7 +1541,7 @@
         <v>0.175</v>
       </c>
       <c r="D80" t="n">
-        <v>0.6094994872887947</v>
+        <v>0.6267927650567272</v>
       </c>
     </row>
     <row r="81">
@@ -1569,7 +1569,7 @@
         <v>0.225</v>
       </c>
       <c r="D82" t="n">
-        <v>0.6801495137099186</v>
+        <v>0.6898858525424121</v>
       </c>
     </row>
     <row r="83">
@@ -1583,7 +1583,7 @@
         <v>0.25</v>
       </c>
       <c r="D83" t="n">
-        <v>0.6974547825201964</v>
+        <v>0.7094289757721294</v>
       </c>
     </row>
     <row r="84">
@@ -1597,7 +1597,7 @@
         <v>0.275</v>
       </c>
       <c r="D84" t="n">
-        <v>0.7147600513304743</v>
+        <v>0.7229850023758799</v>
       </c>
     </row>
     <row r="85">
@@ -1625,7 +1625,7 @@
         <v>0.325</v>
       </c>
       <c r="D86" t="n">
-        <v>0.7390433183360505</v>
+        <v>0.738276942703345</v>
       </c>
     </row>
     <row r="87">
@@ -1639,7 +1639,7 @@
         <v>0.35</v>
       </c>
       <c r="D87" t="n">
-        <v>0.746021316531349</v>
+        <v>0.7436093870983037</v>
       </c>
     </row>
     <row r="88">
@@ -1653,7 +1653,7 @@
         <v>0.375</v>
       </c>
       <c r="D88" t="n">
-        <v>0.7529993147266475</v>
+        <v>0.7501477962097851</v>
       </c>
     </row>
     <row r="89">
@@ -1681,7 +1681,7 @@
         <v>0.4249999999999999</v>
       </c>
       <c r="D90" t="n">
-        <v>0.7728248135464689</v>
+        <v>0.7742058613995604</v>
       </c>
     </row>
     <row r="91">
@@ -1695,7 +1695,7 @@
         <v>0.45</v>
       </c>
       <c r="D91" t="n">
-        <v>0.785672314170992</v>
+        <v>0.7900324909298728</v>
       </c>
     </row>
     <row r="92">
@@ -1709,7 +1709,7 @@
         <v>0.475</v>
       </c>
       <c r="D92" t="n">
-        <v>0.7985198147955151</v>
+        <v>0.8036790320807449</v>
       </c>
     </row>
     <row r="93">
@@ -1737,7 +1737,7 @@
         <v>0.525</v>
       </c>
       <c r="D94" t="n">
-        <v>0.8027419575303345</v>
+        <v>0.8104112246694049</v>
       </c>
     </row>
     <row r="95">
@@ -1751,7 +1751,7 @@
         <v>0.5499999999999999</v>
       </c>
       <c r="D95" t="n">
-        <v>0.7941165996406309</v>
+        <v>0.8024928561656566</v>
       </c>
     </row>
     <row r="96">
@@ -1765,7 +1765,7 @@
         <v>0.575</v>
       </c>
       <c r="D96" t="n">
-        <v>0.7854912417509271</v>
+        <v>0.7903863593993953</v>
       </c>
     </row>
     <row r="97">
@@ -1793,7 +1793,7 @@
         <v>0.6249999999999999</v>
       </c>
       <c r="D98" t="n">
-        <v>0.7736812088462846</v>
+        <v>0.7647055790417426</v>
       </c>
     </row>
     <row r="99">
@@ -1807,7 +1807,7 @@
         <v>0.6499999999999999</v>
       </c>
       <c r="D99" t="n">
-        <v>0.7704965338313458</v>
+        <v>0.7566795944315551</v>
       </c>
     </row>
     <row r="100">
@@ -1821,7 +1821,7 @@
         <v>0.6749999999999999</v>
       </c>
       <c r="D100" t="n">
-        <v>0.767311858816407</v>
+        <v>0.755562079521263</v>
       </c>
     </row>
     <row r="101">
@@ -1835,7 +1835,7 @@
         <v>0.7</v>
       </c>
       <c r="D101" t="n">
-        <v>0.7641271838014682</v>
+        <v>0.764127183801468</v>
       </c>
     </row>
     <row r="102">
@@ -1863,7 +1863,7 @@
         <v>0.125</v>
       </c>
       <c r="D103" t="n">
-        <v>0.3284423813506493</v>
+        <v>0.3285253842559337</v>
       </c>
     </row>
     <row r="104">
@@ -1877,7 +1877,7 @@
         <v>0.15</v>
       </c>
       <c r="D104" t="n">
-        <v>0.3470408734001342</v>
+        <v>0.3473924082115486</v>
       </c>
     </row>
     <row r="105">
@@ -1891,7 +1891,7 @@
         <v>0.175</v>
       </c>
       <c r="D105" t="n">
-        <v>0.3656393654496191</v>
+        <v>0.3660836647614563</v>
       </c>
     </row>
     <row r="106">
@@ -1919,7 +1919,7 @@
         <v>0.225</v>
       </c>
       <c r="D107" t="n">
-        <v>0.3992429086733384</v>
+        <v>0.4014936900179392</v>
       </c>
     </row>
     <row r="108">
@@ -1933,7 +1933,7 @@
         <v>0.25</v>
       </c>
       <c r="D108" t="n">
-        <v>0.4142479598475727</v>
+        <v>0.417489865911409</v>
       </c>
     </row>
     <row r="109">
@@ -1947,7 +1947,7 @@
         <v>0.275</v>
       </c>
       <c r="D109" t="n">
-        <v>0.4292530110218071</v>
+        <v>0.4318650887729606</v>
       </c>
     </row>
     <row r="110">
@@ -1975,7 +1975,7 @@
         <v>0.325</v>
       </c>
       <c r="D111" t="n">
-        <v>0.4498709144362333</v>
+        <v>0.4543063638019769</v>
       </c>
     </row>
     <row r="112">
@@ -1989,7 +1989,7 @@
         <v>0.35</v>
       </c>
       <c r="D112" t="n">
-        <v>0.4554837666764251</v>
+        <v>0.4616430673236055</v>
       </c>
     </row>
     <row r="113">
@@ -2003,7 +2003,7 @@
         <v>0.375</v>
       </c>
       <c r="D113" t="n">
-        <v>0.461096618916617</v>
+        <v>0.4659001205216439</v>
       </c>
     </row>
     <row r="114">
@@ -2031,7 +2031,7 @@
         <v>0.4249999999999999</v>
       </c>
       <c r="D115" t="n">
-        <v>0.4603197837570228</v>
+        <v>0.4639068469628576</v>
       </c>
     </row>
     <row r="116">
@@ -2045,7 +2045,7 @@
         <v>0.45</v>
       </c>
       <c r="D116" t="n">
-        <v>0.4539300963572367</v>
+        <v>0.4581430955657096</v>
       </c>
     </row>
     <row r="117">
@@ -2059,7 +2059,7 @@
         <v>0.475</v>
       </c>
       <c r="D117" t="n">
-        <v>0.4475404089574506</v>
+        <v>0.4502728445643253</v>
       </c>
     </row>
     <row r="118">
@@ -2087,7 +2087,7 @@
         <v>0.525</v>
       </c>
       <c r="D119" t="n">
-        <v>0.435568855439007</v>
+        <v>0.4317811540763372</v>
       </c>
     </row>
     <row r="120">
@@ -2101,7 +2101,7 @@
         <v>0.5499999999999999</v>
       </c>
       <c r="D120" t="n">
-        <v>0.4299869893203496</v>
+        <v>0.4237677693775515</v>
       </c>
     </row>
     <row r="121">
@@ -2115,7 +2115,7 @@
         <v>0.575</v>
       </c>
       <c r="D121" t="n">
-        <v>0.424405123201692</v>
+        <v>0.4188639946501647</v>
       </c>
     </row>
     <row r="122">
@@ -2143,7 +2143,7 @@
         <v>0.6249999999999999</v>
       </c>
       <c r="D123" t="n">
-        <v>0.4397072483608341</v>
+        <v>0.4253989838650187</v>
       </c>
     </row>
     <row r="124">
@@ -2157,7 +2157,7 @@
         <v>0.6499999999999999</v>
       </c>
       <c r="D124" t="n">
-        <v>0.4605912396386337</v>
+        <v>0.4403446021849748</v>
       </c>
     </row>
     <row r="125">
@@ -2171,7 +2171,7 @@
         <v>0.6749999999999999</v>
       </c>
       <c r="D125" t="n">
-        <v>0.4814752309164333</v>
+        <v>0.4654135392317603</v>
       </c>
     </row>
     <row r="126">
@@ -2213,7 +2213,7 @@
         <v>0.125</v>
       </c>
       <c r="D128" t="n">
-        <v>0.4814872325832248</v>
+        <v>0.4879118876234076</v>
       </c>
     </row>
     <row r="129">
@@ -2227,7 +2227,7 @@
         <v>0.15</v>
       </c>
       <c r="D129" t="n">
-        <v>0.5073082731547939</v>
+        <v>0.5156009719227209</v>
       </c>
     </row>
     <row r="130">
@@ -2241,7 +2241,7 @@
         <v>0.175</v>
       </c>
       <c r="D130" t="n">
-        <v>0.5331293137263631</v>
+        <v>0.5391437068380706</v>
       </c>
     </row>
     <row r="131">
@@ -2269,7 +2269,7 @@
         <v>0.225</v>
       </c>
       <c r="D132" t="n">
-        <v>0.5714680927614499</v>
+        <v>0.575431176230781</v>
       </c>
     </row>
     <row r="133">
@@ -2283,7 +2283,7 @@
         <v>0.25</v>
       </c>
       <c r="D133" t="n">
-        <v>0.5839858312249677</v>
+        <v>0.5889964345650922</v>
       </c>
     </row>
     <row r="134">
@@ -2297,7 +2297,7 @@
         <v>0.275</v>
       </c>
       <c r="D134" t="n">
-        <v>0.5965035696884856</v>
+        <v>0.6000563912293411</v>
       </c>
     </row>
     <row r="135">
@@ -2325,7 +2325,7 @@
         <v>0.325</v>
       </c>
       <c r="D136" t="n">
-        <v>0.6142376689638293</v>
+        <v>0.6162663056116012</v>
       </c>
     </row>
     <row r="137">
@@ -2339,7 +2339,7 @@
         <v>0.35</v>
       </c>
       <c r="D137" t="n">
-        <v>0.6194540297756552</v>
+        <v>0.6220259372868457</v>
       </c>
     </row>
     <row r="138">
@@ -2353,7 +2353,7 @@
         <v>0.375</v>
       </c>
       <c r="D138" t="n">
-        <v>0.6246703905874811</v>
+        <v>0.6264996152064949</v>
       </c>
     </row>
     <row r="139">
@@ -2381,7 +2381,7 @@
         <v>0.4249999999999999</v>
       </c>
       <c r="D140" t="n">
-        <v>0.631091282320925</v>
+        <v>0.6323578009504219</v>
       </c>
     </row>
     <row r="141">
@@ -2395,7 +2395,7 @@
         <v>0.45</v>
       </c>
       <c r="D141" t="n">
-        <v>0.632295813242543</v>
+        <v>0.6339673911705065</v>
       </c>
     </row>
     <row r="142">
@@ -2409,7 +2409,7 @@
         <v>0.475</v>
       </c>
       <c r="D142" t="n">
-        <v>0.6335003441641611</v>
+        <v>0.6347411924266093</v>
       </c>
     </row>
     <row r="143">
@@ -2437,7 +2437,7 @@
         <v>0.525</v>
       </c>
       <c r="D144" t="n">
-        <v>0.6349492726640784</v>
+        <v>0.6340202132385782</v>
       </c>
     </row>
     <row r="145">
@@ -2451,7 +2451,7 @@
         <v>0.5499999999999999</v>
       </c>
       <c r="D145" t="n">
-        <v>0.6351936702423777</v>
+        <v>0.6333933958696235</v>
       </c>
     </row>
     <row r="146">
@@ -2465,7 +2465,7 @@
         <v>0.575</v>
       </c>
       <c r="D146" t="n">
-        <v>0.6354380678206771</v>
+        <v>0.633666715687046</v>
       </c>
     </row>
     <row r="147">
@@ -2493,7 +2493,7 @@
         <v>0.6249999999999999</v>
       </c>
       <c r="D148" t="n">
-        <v>0.6462657533878304</v>
+        <v>0.6402829377135456</v>
       </c>
     </row>
     <row r="149">
@@ -2507,7 +2507,7 @@
         <v>0.6499999999999999</v>
       </c>
       <c r="D149" t="n">
-        <v>0.6568490413766845</v>
+        <v>0.6483104253388841</v>
       </c>
     </row>
     <row r="150">
@@ -2521,7 +2521,7 @@
         <v>0.6749999999999999</v>
       </c>
       <c r="D150" t="n">
-        <v>0.6674323293655386</v>
+        <v>0.6606072209831229</v>
       </c>
     </row>
     <row r="151">
@@ -2563,7 +2563,7 @@
         <v>0.125</v>
       </c>
       <c r="D153" t="n">
-        <v>0.5939542520028818</v>
+        <v>0.6042436467042452</v>
       </c>
     </row>
     <row r="154">
@@ -2577,7 +2577,7 @@
         <v>0.15</v>
       </c>
       <c r="D154" t="n">
-        <v>0.6357159173175061</v>
+        <v>0.6490292730620661</v>
       </c>
     </row>
     <row r="155">
@@ -2591,7 +2591,7 @@
         <v>0.175</v>
       </c>
       <c r="D155" t="n">
-        <v>0.6774775826321304</v>
+        <v>0.6871582215476071</v>
       </c>
     </row>
     <row r="156">
@@ -2619,7 +2619,7 @@
         <v>0.225</v>
       </c>
       <c r="D157" t="n">
-        <v>0.7392442480593522</v>
+        <v>0.7458811080453958</v>
       </c>
     </row>
     <row r="158">
@@ -2633,7 +2633,7 @@
         <v>0.25</v>
       </c>
       <c r="D158" t="n">
-        <v>0.7592492481719497</v>
+        <v>0.7676925576294166</v>
       </c>
     </row>
     <row r="159">
@@ -2647,7 +2647,7 @@
         <v>0.275</v>
       </c>
       <c r="D159" t="n">
-        <v>0.7792542482845473</v>
+        <v>0.785282352484704</v>
       </c>
     </row>
     <row r="160">
@@ -2675,7 +2675,7 @@
         <v>0.325</v>
       </c>
       <c r="D161" t="n">
-        <v>0.8074082819531068</v>
+        <v>0.8102420390320756</v>
       </c>
     </row>
     <row r="162">
@@ -2689,7 +2689,7 @@
         <v>0.35</v>
       </c>
       <c r="D162" t="n">
-        <v>0.8155573155090687</v>
+        <v>0.8188896695726349</v>
       </c>
     </row>
     <row r="163">
@@ -2703,7 +2703,7 @@
         <v>0.375</v>
       </c>
       <c r="D163" t="n">
-        <v>0.8237063490650308</v>
+        <v>0.8258711230814112</v>
       </c>
     </row>
     <row r="164">
@@ -2731,7 +2731,7 @@
         <v>0.4249999999999999</v>
       </c>
       <c r="D165" t="n">
-        <v>0.8359117823374219</v>
+        <v>0.8373376943656493</v>
       </c>
     </row>
     <row r="166">
@@ -2745,7 +2745,7 @@
         <v>0.45</v>
       </c>
       <c r="D166" t="n">
-        <v>0.8399681820538508</v>
+        <v>0.8421183569363723</v>
       </c>
     </row>
     <row r="167">
@@ -2759,7 +2759,7 @@
         <v>0.475</v>
       </c>
       <c r="D167" t="n">
-        <v>0.8440245817702798</v>
+        <v>0.8458239320658346</v>
       </c>
     </row>
     <row r="168">
@@ -2787,7 +2787,7 @@
         <v>0.525</v>
       </c>
       <c r="D169" t="n">
-        <v>0.8469689397736284</v>
+        <v>0.8486485303363022</v>
       </c>
     </row>
     <row r="170">
@@ -2801,7 +2801,7 @@
         <v>0.5499999999999999</v>
       </c>
       <c r="D170" t="n">
-        <v>0.8458568980605481</v>
+        <v>0.8478154573704598</v>
       </c>
     </row>
     <row r="171">
@@ -2815,7 +2815,7 @@
         <v>0.575</v>
       </c>
       <c r="D171" t="n">
-        <v>0.8447448563474678</v>
+        <v>0.8460031047496617</v>
       </c>
     </row>
     <row r="172">
@@ -2843,7 +2843,7 @@
         <v>0.6249999999999999</v>
       </c>
       <c r="D173" t="n">
-        <v>0.8419743915853215</v>
+        <v>0.8411259291851165</v>
       </c>
     </row>
     <row r="174">
@@ -2857,7 +2857,7 @@
         <v>0.6499999999999999</v>
       </c>
       <c r="D174" t="n">
-        <v>0.8403159685362558</v>
+        <v>0.8389037905623293</v>
       </c>
     </row>
     <row r="175">
@@ -2871,7 +2871,7 @@
         <v>0.6749999999999999</v>
       </c>
       <c r="D175" t="n">
-        <v>0.83865754548719</v>
+        <v>0.8373877409265053</v>
       </c>
     </row>
     <row r="176">
@@ -2913,7 +2913,7 @@
         <v>0.125</v>
       </c>
       <c r="D178" t="n">
-        <v>0.6362942230871569</v>
+        <v>0.64659146916301</v>
       </c>
     </row>
     <row r="179">
@@ -2927,7 +2927,7 @@
         <v>0.15</v>
       </c>
       <c r="D179" t="n">
-        <v>0.6819553499590023</v>
+        <v>0.6955022244333449</v>
       </c>
     </row>
     <row r="180">
@@ -2941,7 +2941,7 @@
         <v>0.175</v>
       </c>
       <c r="D180" t="n">
-        <v>0.7276164768308477</v>
+        <v>0.7376395424665083</v>
       </c>
     </row>
     <row r="181">
@@ -2969,7 +2969,7 @@
         <v>0.225</v>
       </c>
       <c r="D182" t="n">
-        <v>0.7940384251473935</v>
+        <v>0.8026905885820916</v>
       </c>
     </row>
     <row r="183">
@@ -2983,7 +2983,7 @@
         <v>0.25</v>
       </c>
       <c r="D183" t="n">
-        <v>0.814799246592094</v>
+        <v>0.8261526775448964</v>
       </c>
     </row>
     <row r="184">
@@ -2997,7 +2997,7 @@
         <v>0.275</v>
       </c>
       <c r="D184" t="n">
-        <v>0.8355600680367945</v>
+        <v>0.8439380510313</v>
       </c>
     </row>
     <row r="185">
@@ -3025,7 +3025,7 @@
         <v>0.325</v>
       </c>
       <c r="D186" t="n">
-        <v>0.861332185450279</v>
+        <v>0.8638731166424328</v>
       </c>
     </row>
     <row r="187">
@@ -3039,7 +3039,7 @@
         <v>0.35</v>
       </c>
       <c r="D187" t="n">
-        <v>0.8663434814190631</v>
+        <v>0.8683576294881028</v>
       </c>
     </row>
     <row r="188">
@@ -3053,7 +3053,7 @@
         <v>0.375</v>
       </c>
       <c r="D188" t="n">
-        <v>0.8713547773878473</v>
+        <v>0.8718350682992529</v>
       </c>
     </row>
     <row r="189">
@@ -3081,7 +3081,7 @@
         <v>0.4249999999999999</v>
       </c>
       <c r="D190" t="n">
-        <v>0.8831593986318275</v>
+        <v>0.883344110140893</v>
       </c>
     </row>
     <row r="191">
@@ -3095,7 +3095,7 @@
         <v>0.45</v>
       </c>
       <c r="D191" t="n">
-        <v>0.8899527239070235</v>
+        <v>0.8914939449323189</v>
       </c>
     </row>
     <row r="192">
@@ -3109,7 +3109,7 @@
         <v>0.475</v>
       </c>
       <c r="D192" t="n">
-        <v>0.8967460491822196</v>
+        <v>0.8988731692110972</v>
       </c>
     </row>
     <row r="193">
@@ -3137,7 +3137,7 @@
         <v>0.525</v>
       </c>
       <c r="D194" t="n">
-        <v>0.8996911600173941</v>
+        <v>0.904048912807329</v>
       </c>
     </row>
     <row r="195">
@@ -3151,7 +3151,7 @@
         <v>0.5499999999999999</v>
       </c>
       <c r="D195" t="n">
-        <v>0.8958429455773728</v>
+        <v>0.9009531790203597</v>
       </c>
     </row>
     <row r="196">
@@ -3165,7 +3165,7 @@
         <v>0.575</v>
       </c>
       <c r="D196" t="n">
-        <v>0.8919947311373514</v>
+        <v>0.8953023285118969</v>
       </c>
     </row>
     <row r="197">
@@ -3193,7 +3193,7 @@
         <v>0.6249999999999999</v>
       </c>
       <c r="D198" t="n">
-        <v>0.8824790786944492</v>
+        <v>0.8805358989920483</v>
       </c>
     </row>
     <row r="199">
@@ -3207,7 +3207,7 @@
         <v>0.6499999999999999</v>
       </c>
       <c r="D199" t="n">
-        <v>0.8768116406915684</v>
+        <v>0.8735206308114409</v>
       </c>
     </row>
     <row r="200">
@@ -3221,7 +3221,7 @@
         <v>0.6749999999999999</v>
       </c>
       <c r="D200" t="n">
-        <v>0.8711442026886876</v>
+        <v>0.8681508675708974</v>
       </c>
     </row>
     <row r="201">
@@ -3263,7 +3263,7 @@
         <v>0.125</v>
       </c>
       <c r="D203" t="n">
-        <v>0.4054272148225037</v>
+        <v>0.4123693986973184</v>
       </c>
     </row>
     <row r="204">
@@ -3277,7 +3277,7 @@
         <v>0.15</v>
       </c>
       <c r="D204" t="n">
-        <v>0.4348640302801617</v>
+        <v>0.4438501190149184</v>
       </c>
     </row>
     <row r="205">
@@ -3291,7 +3291,7 @@
         <v>0.175</v>
       </c>
       <c r="D205" t="n">
-        <v>0.4643008457378197</v>
+        <v>0.4708377949651401</v>
       </c>
     </row>
     <row r="206">
@@ -3319,7 +3319,7 @@
         <v>0.225</v>
       </c>
       <c r="D207" t="n">
-        <v>0.508444176363577</v>
+        <v>0.5129549523534257</v>
       </c>
     </row>
     <row r="208">
@@ -3333,7 +3333,7 @@
         <v>0.25</v>
       </c>
       <c r="D208" t="n">
-        <v>0.5231506915316763</v>
+        <v>0.5288949030864784</v>
       </c>
     </row>
     <row r="209">
@@ -3347,7 +3347,7 @@
         <v>0.275</v>
       </c>
       <c r="D209" t="n">
-        <v>0.5378572066997755</v>
+        <v>0.54196274804213</v>
       </c>
     </row>
     <row r="210">
@@ -3375,7 +3375,7 @@
         <v>0.325</v>
       </c>
       <c r="D211" t="n">
-        <v>0.5586610050221956</v>
+        <v>0.5610803913309492</v>
       </c>
     </row>
     <row r="212">
@@ -3389,7 +3389,7 @@
         <v>0.35</v>
       </c>
       <c r="D212" t="n">
-        <v>0.5647582881765164</v>
+        <v>0.5678046516775574</v>
       </c>
     </row>
     <row r="213">
@@ -3403,7 +3403,7 @@
         <v>0.375</v>
       </c>
       <c r="D213" t="n">
-        <v>0.5708555713308373</v>
+        <v>0.573005730273645</v>
       </c>
     </row>
     <row r="214">
@@ -3431,7 +3431,7 @@
         <v>0.4249999999999999</v>
       </c>
       <c r="D215" t="n">
-        <v>0.5788960334447611</v>
+        <v>0.5799018019205299</v>
       </c>
     </row>
     <row r="216">
@@ -3445,7 +3445,7 @@
         <v>0.45</v>
       </c>
       <c r="D216" t="n">
-        <v>0.5808392124043641</v>
+        <v>0.5820545511581428</v>
       </c>
     </row>
     <row r="217">
@@ -3459,7 +3459,7 @@
         <v>0.475</v>
       </c>
       <c r="D217" t="n">
-        <v>0.5827823913639671</v>
+        <v>0.5835996310188662</v>
       </c>
     </row>
     <row r="218">
@@ -3487,7 +3487,7 @@
         <v>0.525</v>
       </c>
       <c r="D219" t="n">
-        <v>0.5854358507855025</v>
+        <v>0.5856014946708071</v>
       </c>
     </row>
     <row r="220">
@@ -3501,7 +3501,7 @@
         <v>0.5499999999999999</v>
       </c>
       <c r="D220" t="n">
-        <v>0.5861461312474349</v>
+        <v>0.5863189167698624</v>
       </c>
     </row>
     <row r="221">
@@ -3515,7 +3515,7 @@
         <v>0.575</v>
       </c>
       <c r="D221" t="n">
-        <v>0.5868564117093673</v>
+        <v>0.5869499461077038</v>
       </c>
     </row>
     <row r="222">
@@ -3543,7 +3543,7 @@
         <v>0.6249999999999999</v>
       </c>
       <c r="D223" t="n">
-        <v>0.5885082774841224</v>
+        <v>0.5882412644476182</v>
       </c>
     </row>
     <row r="224">
@@ -3557,7 +3557,7 @@
         <v>0.6499999999999999</v>
       </c>
       <c r="D224" t="n">
-        <v>0.5894498627969452</v>
+        <v>0.5890457724236273</v>
       </c>
     </row>
     <row r="225">
@@ -3571,7 +3571,7 @@
         <v>0.6749999999999999</v>
       </c>
       <c r="D225" t="n">
-        <v>0.590391448109768</v>
+        <v>0.5900523255862956</v>
       </c>
     </row>
     <row r="226">
@@ -3613,7 +3613,7 @@
         <v>0.125</v>
       </c>
       <c r="D228" t="n">
-        <v>0.5676930230252196</v>
+        <v>0.5774199869741546</v>
       </c>
     </row>
     <row r="229">
@@ -3627,7 +3627,7 @@
         <v>0.15</v>
       </c>
       <c r="D229" t="n">
-        <v>0.602127987171222</v>
+        <v>0.6145975884299644</v>
       </c>
     </row>
     <row r="230">
@@ -3641,7 +3641,7 @@
         <v>0.175</v>
       </c>
       <c r="D230" t="n">
-        <v>0.6365629513172244</v>
+        <v>0.6455403892564028</v>
       </c>
     </row>
     <row r="231">
@@ -3669,7 +3669,7 @@
         <v>0.225</v>
       </c>
       <c r="D232" t="n">
-        <v>0.6864898851697978</v>
+        <v>0.691719693060193</v>
       </c>
     </row>
     <row r="233">
@@ -3683,7 +3683,7 @@
         <v>0.25</v>
       </c>
       <c r="D233" t="n">
-        <v>0.7019818548763689</v>
+        <v>0.708455248057058</v>
       </c>
     </row>
     <row r="234">
@@ -3697,7 +3697,7 @@
         <v>0.275</v>
       </c>
       <c r="D234" t="n">
-        <v>0.71747382458294</v>
+        <v>0.7219541064635784</v>
       </c>
     </row>
     <row r="235">
@@ -3725,7 +3725,7 @@
         <v>0.325</v>
       </c>
       <c r="D236" t="n">
-        <v>0.7389284405636437</v>
+        <v>0.7420786659727926</v>
       </c>
     </row>
     <row r="237">
@@ -3739,7 +3739,7 @@
         <v>0.35</v>
       </c>
       <c r="D237" t="n">
-        <v>0.7448910868377764</v>
+        <v>0.7492363896640822</v>
       </c>
     </row>
     <row r="238">
@@ -3753,7 +3753,7 @@
         <v>0.375</v>
       </c>
       <c r="D238" t="n">
-        <v>0.7508537331119092</v>
+        <v>0.7542214619422191</v>
       </c>
     </row>
     <row r="239">
@@ -3781,7 +3781,7 @@
         <v>0.4249999999999999</v>
       </c>
       <c r="D240" t="n">
-        <v>0.7559784448318729</v>
+        <v>0.7570305168364901</v>
       </c>
     </row>
     <row r="241">
@@ -3795,7 +3795,7 @@
         <v>0.45</v>
       </c>
       <c r="D241" t="n">
-        <v>0.7551405102777038</v>
+        <v>0.7557807621829014</v>
       </c>
     </row>
     <row r="242">
@@ -3809,7 +3809,7 @@
         <v>0.475</v>
       </c>
       <c r="D242" t="n">
-        <v>0.7543025757235348</v>
+        <v>0.7542108815767139</v>
       </c>
     </row>
     <row r="243">
@@ -3837,7 +3837,7 @@
         <v>0.525</v>
       </c>
       <c r="D244" t="n">
-        <v>0.7562183690616407</v>
+        <v>0.7544184344276278</v>
       </c>
     </row>
     <row r="245">
@@ -3851,7 +3851,7 @@
         <v>0.5499999999999999</v>
       </c>
       <c r="D245" t="n">
-        <v>0.7589720969539159</v>
+        <v>0.756879164079606</v>
       </c>
     </row>
     <row r="246">
@@ -3865,7 +3865,7 @@
         <v>0.575</v>
       </c>
       <c r="D246" t="n">
-        <v>0.761725824846191</v>
+        <v>0.7603863601687392</v>
       </c>
     </row>
     <row r="247">
@@ -3893,7 +3893,7 @@
         <v>0.6249999999999999</v>
       </c>
       <c r="D248" t="n">
-        <v>0.7677353867268722</v>
+        <v>0.7686982718322257</v>
       </c>
     </row>
     <row r="249">
@@ -3907,7 +3907,7 @@
         <v>0.6499999999999999</v>
       </c>
       <c r="D249" t="n">
-        <v>0.7709912207152784</v>
+        <v>0.7725820474934572</v>
       </c>
     </row>
     <row r="250">
@@ -3921,7 +3921,7 @@
         <v>0.6749999999999999</v>
       </c>
       <c r="D250" t="n">
-        <v>0.7742470547036845</v>
+        <v>0.7756704097655991</v>
       </c>
     </row>
     <row r="251">
@@ -3963,7 +3963,7 @@
         <v>0.125</v>
       </c>
       <c r="D253" t="n">
-        <v>0.6811269076322046</v>
+        <v>0.6945435138282005</v>
       </c>
     </row>
     <row r="254">
@@ -3977,7 +3977,7 @@
         <v>0.15</v>
       </c>
       <c r="D254" t="n">
-        <v>0.7263939870514672</v>
+        <v>0.7435708241939861</v>
       </c>
     </row>
     <row r="255">
@@ -3991,7 +3991,7 @@
         <v>0.175</v>
       </c>
       <c r="D255" t="n">
-        <v>0.7716610664707296</v>
+        <v>0.7840097159885124</v>
       </c>
     </row>
     <row r="256">
@@ -4019,7 +4019,7 @@
         <v>0.225</v>
       </c>
       <c r="D257" t="n">
-        <v>0.8363852044499214</v>
+        <v>0.8433940705766386</v>
       </c>
     </row>
     <row r="258">
@@ -4033,7 +4033,7 @@
         <v>0.25</v>
       </c>
       <c r="D258" t="n">
-        <v>0.8558422630098506</v>
+        <v>0.8644754467266649</v>
       </c>
     </row>
     <row r="259">
@@ -4047,7 +4047,7 @@
         <v>0.275</v>
       </c>
       <c r="D259" t="n">
-        <v>0.8752993215697797</v>
+        <v>0.8812402310182839</v>
       </c>
     </row>
     <row r="260">
@@ -4075,7 +4075,7 @@
         <v>0.325</v>
       </c>
       <c r="D261" t="n">
-        <v>0.9035286056891217</v>
+        <v>0.9059692183021157</v>
       </c>
     </row>
     <row r="262">
@@ -4089,7 +4089,7 @@
         <v>0.35</v>
       </c>
       <c r="D262" t="n">
-        <v>0.9123008312485347</v>
+        <v>0.9153335400285326</v>
       </c>
     </row>
     <row r="263">
@@ -4103,7 +4103,7 @@
         <v>0.375</v>
       </c>
       <c r="D263" t="n">
-        <v>0.9210730568079477</v>
+        <v>0.9231815073649506</v>
       </c>
     </row>
     <row r="264">
@@ -4131,7 +4131,7 @@
         <v>0.4249999999999999</v>
       </c>
       <c r="D265" t="n">
-        <v>0.9338799917987155</v>
+        <v>0.9355739399032543</v>
       </c>
     </row>
     <row r="266">
@@ -4145,7 +4145,7 @@
         <v>0.45</v>
       </c>
       <c r="D266" t="n">
-        <v>0.9379147012300705</v>
+        <v>0.9402842060861257</v>
       </c>
     </row>
     <row r="267">
@@ -4159,7 +4159,7 @@
         <v>0.475</v>
       </c>
       <c r="D267" t="n">
-        <v>0.9419494106614253</v>
+        <v>0.9438097198409695</v>
       </c>
     </row>
     <row r="268">
@@ -4187,7 +4187,7 @@
         <v>0.525</v>
       </c>
       <c r="D269" t="n">
-        <v>0.9452932823310501</v>
+        <v>0.9467250677114948</v>
       </c>
     </row>
     <row r="270">
@@ -4201,7 +4201,7 @@
         <v>0.5499999999999999</v>
       </c>
       <c r="D270" t="n">
-        <v>0.94460244456932</v>
+        <v>0.946286311346816</v>
       </c>
     </row>
     <row r="271">
@@ -4215,7 +4215,7 @@
         <v>0.575</v>
       </c>
       <c r="D271" t="n">
-        <v>0.9439116068075898</v>
+        <v>0.9450056215933892</v>
       </c>
     </row>
     <row r="272">
@@ -4243,7 +4243,7 @@
         <v>0.6249999999999999</v>
       </c>
       <c r="D273" t="n">
-        <v>0.9418643624862985</v>
+        <v>0.9412695242988723</v>
       </c>
     </row>
     <row r="274">
@@ -4257,7 +4257,7 @@
         <v>0.6499999999999999</v>
       </c>
       <c r="D274" t="n">
-        <v>0.9405079559267373</v>
+        <v>0.9394896579470723</v>
       </c>
     </row>
     <row r="275">
@@ -4271,7 +4271,7 @@
         <v>0.6749999999999999</v>
       </c>
       <c r="D275" t="n">
-        <v>0.9391515493671762</v>
+        <v>0.9382189405851048</v>
       </c>
     </row>
     <row r="276">
@@ -4313,7 +4313,7 @@
         <v>0.125</v>
       </c>
       <c r="D278" t="n">
-        <v>0.7181394806656203</v>
+        <v>0.7343681565353751</v>
       </c>
     </row>
     <row r="279">
@@ -4327,7 +4327,7 @@
         <v>0.15</v>
       </c>
       <c r="D279" t="n">
-        <v>0.7680512487756118</v>
+        <v>0.7887945082845573</v>
       </c>
     </row>
     <row r="280">
@@ -4341,7 +4341,7 @@
         <v>0.175</v>
       </c>
       <c r="D280" t="n">
-        <v>0.8179630168856032</v>
+        <v>0.8328492302792668</v>
       </c>
     </row>
     <row r="281">
@@ -4369,7 +4369,7 @@
         <v>0.225</v>
       </c>
       <c r="D282" t="n">
-        <v>0.8870397338964254</v>
+        <v>0.8952136349096325</v>
       </c>
     </row>
     <row r="283">
@@ -4383,7 +4383,7 @@
         <v>0.25</v>
       </c>
       <c r="D283" t="n">
-        <v>0.9062046827972561</v>
+        <v>0.9162082424974712</v>
       </c>
     </row>
     <row r="284">
@@ -4397,7 +4397,7 @@
         <v>0.275</v>
       </c>
       <c r="D284" t="n">
-        <v>0.9253696316980866</v>
+        <v>0.9322010702352025</v>
       </c>
     </row>
     <row r="285">
@@ -4425,7 +4425,7 @@
         <v>0.325</v>
       </c>
       <c r="D286" t="n">
-        <v>0.9522647450732503</v>
+        <v>0.9544157757625321</v>
       </c>
     </row>
     <row r="287">
@@ -4439,7 +4439,7 @@
         <v>0.35</v>
       </c>
       <c r="D287" t="n">
-        <v>0.9599949095475835</v>
+        <v>0.9625098166912641</v>
       </c>
     </row>
     <row r="288">
@@ -4453,7 +4453,7 @@
         <v>0.375</v>
       </c>
       <c r="D288" t="n">
-        <v>0.9677250740219165</v>
+        <v>0.9693464040481559</v>
       </c>
     </row>
     <row r="289">
@@ -4481,7 +4481,7 @@
         <v>0.4249999999999999</v>
       </c>
       <c r="D290" t="n">
-        <v>0.9804583733316157</v>
+        <v>0.9812450944075913</v>
       </c>
     </row>
     <row r="291">
@@ -4495,7 +4495,7 @@
         <v>0.45</v>
       </c>
       <c r="D291" t="n">
-        <v>0.9854615081669816</v>
+        <v>0.9866410409902404</v>
       </c>
     </row>
     <row r="292">
@@ -4509,7 +4509,7 @@
         <v>0.475</v>
       </c>
       <c r="D292" t="n">
-        <v>0.9904646430023476</v>
+        <v>0.9914472211612601</v>
       </c>
     </row>
     <row r="293">
@@ -4537,7 +4537,7 @@
         <v>0.525</v>
       </c>
       <c r="D294" t="n">
-        <v>0.9966008333782852</v>
+        <v>0.998510344125115</v>
       </c>
     </row>
     <row r="295">
@@ -4551,7 +4551,7 @@
         <v>0.5499999999999999</v>
       </c>
       <c r="D295" t="n">
-        <v>0.9977338889188567</v>
+        <v>1</v>
       </c>
     </row>
     <row r="296">
@@ -4565,7 +4565,7 @@
         <v>0.575</v>
       </c>
       <c r="D296" t="n">
-        <v>0.9988669444594284</v>
+        <v>1</v>
       </c>
     </row>
     <row r="297">
@@ -4593,7 +4593,7 @@
         <v>0.6249999999999999</v>
       </c>
       <c r="D298" t="n">
-        <v>0.9944084779948785</v>
+        <v>0.9973674844550885</v>
       </c>
     </row>
     <row r="299">
@@ -4607,7 +4607,7 @@
         <v>0.6499999999999999</v>
       </c>
       <c r="D299" t="n">
-        <v>0.9888169559897569</v>
+        <v>0.9928789085715235</v>
       </c>
     </row>
     <row r="300">
@@ -4621,7 +4621,7 @@
         <v>0.6749999999999999</v>
       </c>
       <c r="D300" t="n">
-        <v>0.9832254339846355</v>
+        <v>0.9863593563970755</v>
       </c>
     </row>
     <row r="301">

--- a/data/processed/interpolated_data.xlsx
+++ b/data/processed/interpolated_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D301"/>
+  <dimension ref="A1:D401"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,10 +446,10 @@
         <v>-2.302585092994045</v>
       </c>
       <c r="C2" t="n">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="D2" t="n">
-        <v>0.172480928696832</v>
+        <v>0.2707138521114459</v>
       </c>
     </row>
     <row r="3">
@@ -460,10 +460,10 @@
         <v>-2.302585092994045</v>
       </c>
       <c r="C3" t="n">
-        <v>0.125</v>
+        <v>0.07291666666666667</v>
       </c>
       <c r="D3" t="n">
-        <v>0.2067495718606536</v>
+        <v>0.2834655271751188</v>
       </c>
     </row>
     <row r="4">
@@ -474,10 +474,10 @@
         <v>-2.302585092994045</v>
       </c>
       <c r="C4" t="n">
-        <v>0.15</v>
+        <v>0.09583333333333333</v>
       </c>
       <c r="D4" t="n">
-        <v>0.235750272507586</v>
+        <v>0.2923015091980364</v>
       </c>
     </row>
     <row r="5">
@@ -488,10 +488,10 @@
         <v>-2.302585092994045</v>
       </c>
       <c r="C5" t="n">
-        <v>0.175</v>
+        <v>0.11875</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2600179173455849</v>
+        <v>0.2992769170757314</v>
       </c>
     </row>
     <row r="6">
@@ -502,10 +502,10 @@
         <v>-2.302585092994045</v>
       </c>
       <c r="C6" t="n">
-        <v>0.2</v>
+        <v>0.1416666666666667</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2800873930826058</v>
+        <v>0.3064468697037365</v>
       </c>
     </row>
     <row r="7">
@@ -516,10 +516,10 @@
         <v>-2.302585092994045</v>
       </c>
       <c r="C7" t="n">
-        <v>0.225</v>
+        <v>0.1645833333333333</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2964935864266043</v>
+        <v>0.3156669934169145</v>
       </c>
     </row>
     <row r="8">
@@ -530,10 +530,10 @@
         <v>-2.302585092994045</v>
       </c>
       <c r="C8" t="n">
-        <v>0.25</v>
+        <v>0.1875</v>
       </c>
       <c r="D8" t="n">
-        <v>0.3097713840855361</v>
+        <v>0.3261989296504543</v>
       </c>
     </row>
     <row r="9">
@@ -544,10 +544,10 @@
         <v>-2.302585092994045</v>
       </c>
       <c r="C9" t="n">
-        <v>0.275</v>
+        <v>0.2104166666666666</v>
       </c>
       <c r="D9" t="n">
-        <v>0.3204556727673567</v>
+        <v>0.3355410366585593</v>
       </c>
     </row>
     <row r="10">
@@ -558,10 +558,10 @@
         <v>-2.302585092994045</v>
       </c>
       <c r="C10" t="n">
-        <v>0.3</v>
+        <v>0.2333333333333333</v>
       </c>
       <c r="D10" t="n">
-        <v>0.3290813391800217</v>
+        <v>0.3426147540061814</v>
       </c>
     </row>
     <row r="11">
@@ -572,10 +572,10 @@
         <v>-2.302585092994045</v>
       </c>
       <c r="C11" t="n">
-        <v>0.325</v>
+        <v>0.25625</v>
       </c>
       <c r="D11" t="n">
-        <v>0.3361683384894501</v>
+        <v>0.3479676767095796</v>
       </c>
     </row>
     <row r="12">
@@ -586,10 +586,10 @@
         <v>-2.302585092994045</v>
       </c>
       <c r="C12" t="n">
-        <v>0.35</v>
+        <v>0.2791666666666667</v>
       </c>
       <c r="D12" t="n">
-        <v>0.3421768996934139</v>
+        <v>0.3504672057320695</v>
       </c>
     </row>
     <row r="13">
@@ -600,10 +600,10 @@
         <v>-2.302585092994045</v>
       </c>
       <c r="C13" t="n">
-        <v>0.375</v>
+        <v>0.3020833333333333</v>
       </c>
       <c r="D13" t="n">
-        <v>0.3475523202476483</v>
+        <v>0.3457575238865163</v>
       </c>
     </row>
     <row r="14">
@@ -614,10 +614,10 @@
         <v>-2.302585092994045</v>
       </c>
       <c r="C14" t="n">
-        <v>0.4</v>
+        <v>0.325</v>
       </c>
       <c r="D14" t="n">
-        <v>0.3527398976078889</v>
+        <v>0.3350327497240966</v>
       </c>
     </row>
     <row r="15">
@@ -628,10 +628,10 @@
         <v>-2.302585092994045</v>
       </c>
       <c r="C15" t="n">
-        <v>0.4249999999999999</v>
+        <v>0.3479166666666667</v>
       </c>
       <c r="D15" t="n">
-        <v>0.3579247884748993</v>
+        <v>0.3374712096089714</v>
       </c>
     </row>
     <row r="16">
@@ -642,10 +642,10 @@
         <v>-2.302585092994045</v>
       </c>
       <c r="C16" t="n">
-        <v>0.45</v>
+        <v>0.3708333333333333</v>
       </c>
       <c r="D16" t="n">
-        <v>0.362251586529558</v>
+        <v>0.3681800872486616</v>
       </c>
     </row>
     <row r="17">
@@ -656,10 +656,10 @@
         <v>-2.302585092994045</v>
       </c>
       <c r="C17" t="n">
-        <v>0.475</v>
+        <v>0.39375</v>
       </c>
       <c r="D17" t="n">
-        <v>0.3646047446977715</v>
+        <v>0.4028640770211236</v>
       </c>
     </row>
     <row r="18">
@@ -670,10 +670,10 @@
         <v>-2.302585092994045</v>
       </c>
       <c r="C18" t="n">
-        <v>0.5</v>
+        <v>0.4166666666666666</v>
       </c>
       <c r="D18" t="n">
-        <v>0.3638687159054468</v>
+        <v>0.4082472058723117</v>
       </c>
     </row>
     <row r="19">
@@ -684,10 +684,10 @@
         <v>-2.302585092994045</v>
       </c>
       <c r="C19" t="n">
-        <v>0.525</v>
+        <v>0.4395833333333333</v>
       </c>
       <c r="D19" t="n">
-        <v>0.3594621784283629</v>
+        <v>0.3879864654966431</v>
       </c>
     </row>
     <row r="20">
@@ -698,10 +698,10 @@
         <v>-2.302585092994045</v>
       </c>
       <c r="C20" t="n">
-        <v>0.5499999999999999</v>
+        <v>0.4625</v>
       </c>
       <c r="D20" t="n">
-        <v>0.3529407119417888</v>
+        <v>0.3653965496512562</v>
       </c>
     </row>
     <row r="21">
@@ -712,10 +712,10 @@
         <v>-2.302585092994045</v>
       </c>
       <c r="C21" t="n">
-        <v>0.575</v>
+        <v>0.4854166666666666</v>
       </c>
       <c r="D21" t="n">
-        <v>0.3463941214708658</v>
+        <v>0.3530825276951344</v>
       </c>
     </row>
     <row r="22">
@@ -726,10 +726,10 @@
         <v>-2.302585092994045</v>
       </c>
       <c r="C22" t="n">
-        <v>0.6</v>
+        <v>0.5083333333333333</v>
       </c>
       <c r="D22" t="n">
-        <v>0.3419122120407355</v>
+        <v>0.3538651523476035</v>
       </c>
     </row>
     <row r="23">
@@ -740,10 +740,10 @@
         <v>-2.302585092994045</v>
       </c>
       <c r="C23" t="n">
-        <v>0.6249999999999999</v>
+        <v>0.53125</v>
       </c>
       <c r="D23" t="n">
-        <v>0.3415847886765391</v>
+        <v>0.3659025487137623</v>
       </c>
     </row>
     <row r="24">
@@ -754,10 +754,10 @@
         <v>-2.302585092994045</v>
       </c>
       <c r="C24" t="n">
-        <v>0.6499999999999999</v>
+        <v>0.5541666666666667</v>
       </c>
       <c r="D24" t="n">
-        <v>0.3475016564034179</v>
+        <v>0.3811674670540205</v>
       </c>
     </row>
     <row r="25">
@@ -768,10 +768,10 @@
         <v>-2.302585092994045</v>
       </c>
       <c r="C25" t="n">
-        <v>0.6749999999999999</v>
+        <v>0.5770833333333334</v>
       </c>
       <c r="D25" t="n">
-        <v>0.3617526202465134</v>
+        <v>0.3911569662449925</v>
       </c>
     </row>
     <row r="26">
@@ -782,10 +782,10 @@
         <v>-2.302585092994045</v>
       </c>
       <c r="C26" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="D26" t="n">
-        <v>0.386427485230967</v>
+        <v>0.3873681051632923</v>
       </c>
     </row>
     <row r="27">
@@ -793,13 +793,13 @@
         <v>0.0007558578987150416</v>
       </c>
       <c r="B27" t="n">
-        <v>0</v>
+        <v>4.440892098500626e-16</v>
       </c>
       <c r="C27" t="n">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="D27" t="n">
-        <v>0.2954766721638665</v>
+        <v>0.3483506669381975</v>
       </c>
     </row>
     <row r="28">
@@ -807,13 +807,13 @@
         <v>0.0007558578987150416</v>
       </c>
       <c r="B28" t="n">
-        <v>0</v>
+        <v>4.440892098500626e-16</v>
       </c>
       <c r="C28" t="n">
-        <v>0.125</v>
+        <v>0.07291666666666667</v>
       </c>
       <c r="D28" t="n">
-        <v>0.3436900825309346</v>
+        <v>0.3815232902392985</v>
       </c>
     </row>
     <row r="29">
@@ -821,13 +821,13 @@
         <v>0.0007558578987150416</v>
       </c>
       <c r="B29" t="n">
-        <v>0</v>
+        <v>4.440892098500626e-16</v>
       </c>
       <c r="C29" t="n">
-        <v>0.15</v>
+        <v>0.09583333333333333</v>
       </c>
       <c r="D29" t="n">
-        <v>0.3826567651247872</v>
+        <v>0.4046044216242892</v>
       </c>
     </row>
     <row r="30">
@@ -835,13 +835,13 @@
         <v>0.0007558578987150416</v>
       </c>
       <c r="B30" t="n">
-        <v>0</v>
+        <v>4.440892098500626e-16</v>
       </c>
       <c r="C30" t="n">
-        <v>0.175</v>
+        <v>0.11875</v>
       </c>
       <c r="D30" t="n">
-        <v>0.4137656364582796</v>
+        <v>0.4198511579760014</v>
       </c>
     </row>
     <row r="31">
@@ -849,13 +849,13 @@
         <v>0.0007558578987150416</v>
       </c>
       <c r="B31" t="n">
-        <v>0</v>
+        <v>4.440892098500626e-16</v>
       </c>
       <c r="C31" t="n">
-        <v>0.2</v>
+        <v>0.1416666666666667</v>
       </c>
       <c r="D31" t="n">
-        <v>0.4384056130442668</v>
+        <v>0.4295205961772671</v>
       </c>
     </row>
     <row r="32">
@@ -863,13 +863,13 @@
         <v>0.0007558578987150416</v>
       </c>
       <c r="B32" t="n">
-        <v>0</v>
+        <v>4.440892098500626e-16</v>
       </c>
       <c r="C32" t="n">
-        <v>0.225</v>
+        <v>0.1645833333333333</v>
       </c>
       <c r="D32" t="n">
-        <v>0.4579656113956041</v>
+        <v>0.4359646487781266</v>
       </c>
     </row>
     <row r="33">
@@ -877,13 +877,13 @@
         <v>0.0007558578987150416</v>
       </c>
       <c r="B33" t="n">
-        <v>0</v>
+        <v>4.440892098500626e-16</v>
       </c>
       <c r="C33" t="n">
-        <v>0.25</v>
+        <v>0.1875</v>
       </c>
       <c r="D33" t="n">
-        <v>0.4738345480251466</v>
+        <v>0.4427681084328478</v>
       </c>
     </row>
     <row r="34">
@@ -891,13 +891,13 @@
         <v>0.0007558578987150416</v>
       </c>
       <c r="B34" t="n">
-        <v>0</v>
+        <v>4.440892098500626e-16</v>
       </c>
       <c r="C34" t="n">
-        <v>0.275</v>
+        <v>0.2104166666666666</v>
       </c>
       <c r="D34" t="n">
-        <v>0.4874013394457495</v>
+        <v>0.4541654960708624</v>
       </c>
     </row>
     <row r="35">
@@ -905,13 +905,13 @@
         <v>0.0007558578987150416</v>
       </c>
       <c r="B35" t="n">
-        <v>0</v>
+        <v>4.440892098500626e-16</v>
       </c>
       <c r="C35" t="n">
-        <v>0.3</v>
+        <v>0.2333333333333333</v>
       </c>
       <c r="D35" t="n">
-        <v>0.5000549021702679</v>
+        <v>0.4682970178670001</v>
       </c>
     </row>
     <row r="36">
@@ -919,13 +919,13 @@
         <v>0.0007558578987150416</v>
       </c>
       <c r="B36" t="n">
-        <v>0</v>
+        <v>4.440892098500626e-16</v>
       </c>
       <c r="C36" t="n">
-        <v>0.325</v>
+        <v>0.25625</v>
       </c>
       <c r="D36" t="n">
-        <v>0.5126794044465336</v>
+        <v>0.4764786095218216</v>
       </c>
     </row>
     <row r="37">
@@ -933,13 +933,13 @@
         <v>0.0007558578987150416</v>
       </c>
       <c r="B37" t="n">
-        <v>0</v>
+        <v>4.440892098500626e-16</v>
       </c>
       <c r="C37" t="n">
-        <v>0.35</v>
+        <v>0.2791666666666667</v>
       </c>
       <c r="D37" t="n">
-        <v>0.5241400214622847</v>
+        <v>0.4752908885349975</v>
       </c>
     </row>
     <row r="38">
@@ -947,13 +947,13 @@
         <v>0.0007558578987150416</v>
       </c>
       <c r="B38" t="n">
-        <v>0</v>
+        <v>4.440892098500626e-16</v>
       </c>
       <c r="C38" t="n">
-        <v>0.375</v>
+        <v>0.3020833333333333</v>
       </c>
       <c r="D38" t="n">
-        <v>0.532797180140235</v>
+        <v>0.4715924933047573</v>
       </c>
     </row>
     <row r="39">
@@ -961,13 +961,13 @@
         <v>0.0007558578987150416</v>
       </c>
       <c r="B39" t="n">
-        <v>0</v>
+        <v>4.440892098500626e-16</v>
       </c>
       <c r="C39" t="n">
-        <v>0.4</v>
+        <v>0.325</v>
       </c>
       <c r="D39" t="n">
-        <v>0.5370113074030994</v>
+        <v>0.4721748705233332</v>
       </c>
     </row>
     <row r="40">
@@ -975,13 +975,13 @@
         <v>0.0007558578987150416</v>
       </c>
       <c r="B40" t="n">
-        <v>0</v>
+        <v>4.440892098500626e-16</v>
       </c>
       <c r="C40" t="n">
-        <v>0.4249999999999999</v>
+        <v>0.3479166666666667</v>
       </c>
       <c r="D40" t="n">
-        <v>0.5357609014009347</v>
+        <v>0.4802862903482477</v>
       </c>
     </row>
     <row r="41">
@@ -989,13 +989,13 @@
         <v>0.0007558578987150416</v>
       </c>
       <c r="B41" t="n">
-        <v>0</v>
+        <v>4.440892098500626e-16</v>
       </c>
       <c r="C41" t="n">
-        <v>0.45</v>
+        <v>0.3708333333333333</v>
       </c>
       <c r="D41" t="n">
-        <v>0.5304967451931673</v>
+        <v>0.4967588202155477</v>
       </c>
     </row>
     <row r="42">
@@ -1003,13 +1003,13 @@
         <v>0.0007558578987150416</v>
       </c>
       <c r="B42" t="n">
-        <v>0</v>
+        <v>4.440892098500626e-16</v>
       </c>
       <c r="C42" t="n">
-        <v>0.475</v>
+        <v>0.39375</v>
       </c>
       <c r="D42" t="n">
-        <v>0.5232876930665664</v>
+        <v>0.5132560615783116</v>
       </c>
     </row>
     <row r="43">
@@ -1017,13 +1017,13 @@
         <v>0.0007558578987150416</v>
       </c>
       <c r="B43" t="n">
-        <v>0</v>
+        <v>4.440892098500626e-16</v>
       </c>
       <c r="C43" t="n">
-        <v>0.5</v>
+        <v>0.4166666666666666</v>
       </c>
       <c r="D43" t="n">
-        <v>0.516202599307901</v>
+        <v>0.5195330794087688</v>
       </c>
     </row>
     <row r="44">
@@ -1031,13 +1031,13 @@
         <v>0.0007558578987150416</v>
       </c>
       <c r="B44" t="n">
-        <v>0</v>
+        <v>4.440892098500626e-16</v>
       </c>
       <c r="C44" t="n">
-        <v>0.525</v>
+        <v>0.4395833333333333</v>
       </c>
       <c r="D44" t="n">
-        <v>0.5109687346446857</v>
+        <v>0.5156409729103792</v>
       </c>
     </row>
     <row r="45">
@@ -1045,13 +1045,13 @@
         <v>0.0007558578987150416</v>
       </c>
       <c r="B45" t="n">
-        <v>0</v>
+        <v>4.440892098500626e-16</v>
       </c>
       <c r="C45" t="n">
-        <v>0.5499999999999999</v>
+        <v>0.4625</v>
       </c>
       <c r="D45" t="n">
-        <v>0.5079470355674165</v>
+        <v>0.5072218541136327</v>
       </c>
     </row>
     <row r="46">
@@ -1059,13 +1059,13 @@
         <v>0.0007558578987150416</v>
       </c>
       <c r="B46" t="n">
-        <v>0</v>
+        <v>4.440892098500626e-16</v>
       </c>
       <c r="C46" t="n">
-        <v>0.575</v>
+        <v>0.4854166666666666</v>
       </c>
       <c r="D46" t="n">
-        <v>0.5071568550073351</v>
+        <v>0.4990148744176218</v>
       </c>
     </row>
     <row r="47">
@@ -1073,13 +1073,13 @@
         <v>0.0007558578987150416</v>
       </c>
       <c r="B47" t="n">
-        <v>0</v>
+        <v>4.440892098500626e-16</v>
       </c>
       <c r="C47" t="n">
-        <v>0.6</v>
+        <v>0.5083333333333333</v>
       </c>
       <c r="D47" t="n">
-        <v>0.5086175458956831</v>
+        <v>0.4948504179282155</v>
       </c>
     </row>
     <row r="48">
@@ -1087,13 +1087,13 @@
         <v>0.0007558578987150416</v>
       </c>
       <c r="B48" t="n">
-        <v>0</v>
+        <v>4.440892098500626e-16</v>
       </c>
       <c r="C48" t="n">
-        <v>0.6249999999999999</v>
+        <v>0.53125</v>
       </c>
       <c r="D48" t="n">
-        <v>0.5123484611637019</v>
+        <v>0.4958243205656425</v>
       </c>
     </row>
     <row r="49">
@@ -1101,13 +1101,13 @@
         <v>0.0007558578987150416</v>
       </c>
       <c r="B49" t="n">
-        <v>0</v>
+        <v>4.440892098500626e-16</v>
       </c>
       <c r="C49" t="n">
-        <v>0.6499999999999999</v>
+        <v>0.5541666666666667</v>
       </c>
       <c r="D49" t="n">
-        <v>0.5183689537426334</v>
+        <v>0.4991645758590638</v>
       </c>
     </row>
     <row r="50">
@@ -1115,13 +1115,13 @@
         <v>0.0007558578987150416</v>
       </c>
       <c r="B50" t="n">
-        <v>0</v>
+        <v>4.440892098500626e-16</v>
       </c>
       <c r="C50" t="n">
-        <v>0.6749999999999999</v>
+        <v>0.5770833333333334</v>
       </c>
       <c r="D50" t="n">
-        <v>0.5266983765637189</v>
+        <v>0.5018017177098075</v>
       </c>
     </row>
     <row r="51">
@@ -1129,13 +1129,13 @@
         <v>0.0007558578987150416</v>
       </c>
       <c r="B51" t="n">
-        <v>0</v>
+        <v>4.440892098500626e-16</v>
       </c>
       <c r="C51" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="D51" t="n">
-        <v>0.5373560825582003</v>
+        <v>0.5006662800192022</v>
       </c>
     </row>
     <row r="52">
@@ -1146,10 +1146,10 @@
         <v>2.302585092994046</v>
       </c>
       <c r="C52" t="n">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="D52" t="n">
-        <v>0.4062520130068391</v>
+        <v>0.4277715320150094</v>
       </c>
     </row>
     <row r="53">
@@ -1160,10 +1160,10 @@
         <v>2.302585092994046</v>
       </c>
       <c r="C53" t="n">
-        <v>0.125</v>
+        <v>0.07291666666666667</v>
       </c>
       <c r="D53" t="n">
-        <v>0.4687693177822853</v>
+        <v>0.5003036499918477</v>
       </c>
     </row>
     <row r="54">
@@ -1174,10 +1174,10 @@
         <v>2.302585092994046</v>
       </c>
       <c r="C54" t="n">
-        <v>0.15</v>
+        <v>0.09583333333333333</v>
       </c>
       <c r="D54" t="n">
-        <v>0.5215644684935141</v>
+        <v>0.5379234958487342</v>
       </c>
     </row>
     <row r="55">
@@ -1188,10 +1188,10 @@
         <v>2.302585092994046</v>
       </c>
       <c r="C55" t="n">
-        <v>0.175</v>
+        <v>0.11875</v>
       </c>
       <c r="D55" t="n">
-        <v>0.5654190952801699</v>
+        <v>0.553844478049206</v>
       </c>
     </row>
     <row r="56">
@@ -1202,10 +1202,10 @@
         <v>2.302585092994046</v>
       </c>
       <c r="C56" t="n">
-        <v>0.2</v>
+        <v>0.1416666666666667</v>
       </c>
       <c r="D56" t="n">
-        <v>0.6011148282818972</v>
+        <v>0.5612800050567999</v>
       </c>
     </row>
     <row r="57">
@@ -1216,10 +1216,10 @@
         <v>2.302585092994046</v>
       </c>
       <c r="C57" t="n">
-        <v>0.225</v>
+        <v>0.1645833333333333</v>
       </c>
       <c r="D57" t="n">
-        <v>0.6294332976383402</v>
+        <v>0.5725368325277224</v>
       </c>
     </row>
     <row r="58">
@@ -1230,10 +1230,10 @@
         <v>2.302585092994046</v>
       </c>
       <c r="C58" t="n">
-        <v>0.25</v>
+        <v>0.1875</v>
       </c>
       <c r="D58" t="n">
-        <v>0.6511561334891438</v>
+        <v>0.588132586320237</v>
       </c>
     </row>
     <row r="59">
@@ -1244,10 +1244,10 @@
         <v>2.302585092994046</v>
       </c>
       <c r="C59" t="n">
-        <v>0.275</v>
+        <v>0.2104166666666666</v>
       </c>
       <c r="D59" t="n">
-        <v>0.6670649659739517</v>
+        <v>0.6005491094761046</v>
       </c>
     </row>
     <row r="60">
@@ -1258,10 +1258,10 @@
         <v>2.302585092994046</v>
       </c>
       <c r="C60" t="n">
-        <v>0.3</v>
+        <v>0.2333333333333333</v>
       </c>
       <c r="D60" t="n">
-        <v>0.6779414252324091</v>
+        <v>0.6081023262301668</v>
       </c>
     </row>
     <row r="61">
@@ -1272,10 +1272,10 @@
         <v>2.302585092994046</v>
       </c>
       <c r="C61" t="n">
-        <v>0.325</v>
+        <v>0.25625</v>
       </c>
       <c r="D61" t="n">
-        <v>0.6848474316985709</v>
+        <v>0.6158343998313258</v>
       </c>
     </row>
     <row r="62">
@@ -1286,10 +1286,10 @@
         <v>2.302585092994046</v>
       </c>
       <c r="C62" t="n">
-        <v>0.35</v>
+        <v>0.2791666666666667</v>
       </c>
       <c r="D62" t="n">
-        <v>0.6899660669841361</v>
+        <v>0.6259006245888621</v>
       </c>
     </row>
     <row r="63">
@@ -1300,10 +1300,10 @@
         <v>2.302585092994046</v>
       </c>
       <c r="C63" t="n">
-        <v>0.375</v>
+        <v>0.3020833333333333</v>
       </c>
       <c r="D63" t="n">
-        <v>0.6957607029952145</v>
+        <v>0.6345302544074127</v>
       </c>
     </row>
     <row r="64">
@@ -1314,10 +1314,10 @@
         <v>2.302585092994046</v>
       </c>
       <c r="C64" t="n">
-        <v>0.4</v>
+        <v>0.325</v>
       </c>
       <c r="D64" t="n">
-        <v>0.704694711637916</v>
+        <v>0.6389636516728032</v>
       </c>
     </row>
     <row r="65">
@@ -1328,10 +1328,10 @@
         <v>2.302585092994046</v>
       </c>
       <c r="C65" t="n">
-        <v>0.4249999999999999</v>
+        <v>0.3479166666666667</v>
       </c>
       <c r="D65" t="n">
-        <v>0.7181865619587344</v>
+        <v>0.6414515657728601</v>
       </c>
     </row>
     <row r="66">
@@ -1342,10 +1342,10 @@
         <v>2.302585092994046</v>
       </c>
       <c r="C66" t="n">
-        <v>0.45</v>
+        <v>0.3708333333333333</v>
       </c>
       <c r="D66" t="n">
-        <v>0.733475111565702</v>
+        <v>0.644662211067447</v>
       </c>
     </row>
     <row r="67">
@@ -1356,10 +1356,10 @@
         <v>2.302585092994046</v>
       </c>
       <c r="C67" t="n">
-        <v>0.475</v>
+        <v>0.39375</v>
       </c>
       <c r="D67" t="n">
-        <v>0.7467543152072342</v>
+        <v>0.6484496981323127</v>
       </c>
     </row>
     <row r="68">
@@ -1370,10 +1370,10 @@
         <v>2.302585092994046</v>
       </c>
       <c r="C68" t="n">
-        <v>0.5</v>
+        <v>0.4166666666666666</v>
       </c>
       <c r="D68" t="n">
-        <v>0.7542181276317472</v>
+        <v>0.6518324933348145</v>
       </c>
     </row>
     <row r="69">
@@ -1384,10 +1384,10 @@
         <v>2.302585092994046</v>
       </c>
       <c r="C69" t="n">
-        <v>0.525</v>
+        <v>0.4395833333333333</v>
       </c>
       <c r="D69" t="n">
-        <v>0.7531706646458832</v>
+        <v>0.654641528087905</v>
       </c>
     </row>
     <row r="70">
@@ -1398,10 +1398,10 @@
         <v>2.302585092994046</v>
       </c>
       <c r="C70" t="n">
-        <v>0.5499999999999999</v>
+        <v>0.4625</v>
       </c>
       <c r="D70" t="n">
-        <v>0.7453566862891893</v>
+        <v>0.657140076529613</v>
       </c>
     </row>
     <row r="71">
@@ -1412,10 +1412,10 @@
         <v>2.302585092994046</v>
       </c>
       <c r="C71" t="n">
-        <v>0.575</v>
+        <v>0.4854166666666666</v>
       </c>
       <c r="D71" t="n">
-        <v>0.7336311136594383</v>
+        <v>0.6593502439466672</v>
       </c>
     </row>
     <row r="72">
@@ -1426,10 +1426,10 @@
         <v>2.302585092994046</v>
       </c>
       <c r="C72" t="n">
-        <v>0.6</v>
+        <v>0.5083333333333333</v>
       </c>
       <c r="D72" t="n">
-        <v>0.7208488678544041</v>
+        <v>0.6610776912688509</v>
       </c>
     </row>
     <row r="73">
@@ -1440,10 +1440,10 @@
         <v>2.302585092994046</v>
       </c>
       <c r="C73" t="n">
-        <v>0.6249999999999999</v>
+        <v>0.53125</v>
       </c>
       <c r="D73" t="n">
-        <v>0.7098648699718594</v>
+        <v>0.6622079640980301</v>
       </c>
     </row>
     <row r="74">
@@ -1454,10 +1454,10 @@
         <v>2.302585092994046</v>
       </c>
       <c r="C74" t="n">
-        <v>0.6499999999999999</v>
+        <v>0.5541666666666667</v>
       </c>
       <c r="D74" t="n">
-        <v>0.7035340411095774</v>
+        <v>0.66275168658598</v>
       </c>
     </row>
     <row r="75">
@@ -1468,10 +1468,10 @@
         <v>2.302585092994046</v>
       </c>
       <c r="C75" t="n">
-        <v>0.6749999999999999</v>
+        <v>0.5770833333333334</v>
       </c>
       <c r="D75" t="n">
-        <v>0.7047113023653317</v>
+        <v>0.6627291021541211</v>
       </c>
     </row>
     <row r="76">
@@ -1482,10 +1482,10 @@
         <v>2.302585092994046</v>
       </c>
       <c r="C76" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="D76" t="n">
-        <v>0.7162515748368952</v>
+        <v>0.662160454223874</v>
       </c>
     </row>
     <row r="77">
@@ -1496,10 +1496,10 @@
         <v>2.70805020110221</v>
       </c>
       <c r="C77" t="n">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="D77" t="n">
-        <v>0.4494652144562564</v>
+        <v>0.4485644587238058</v>
       </c>
     </row>
     <row r="78">
@@ -1510,10 +1510,10 @@
         <v>2.70805020110221</v>
       </c>
       <c r="C78" t="n">
-        <v>0.125</v>
+        <v>0.07291666666666667</v>
       </c>
       <c r="D78" t="n">
-        <v>0.5216146376221229</v>
+        <v>0.5264444820051583</v>
       </c>
     </row>
     <row r="79">
@@ -1524,10 +1524,10 @@
         <v>2.70805020110221</v>
       </c>
       <c r="C79" t="n">
-        <v>0.15</v>
+        <v>0.09583333333333333</v>
       </c>
       <c r="D79" t="n">
-        <v>0.580220025226584</v>
+        <v>0.5695749223989567</v>
       </c>
     </row>
     <row r="80">
@@ -1538,10 +1538,10 @@
         <v>2.70805020110221</v>
       </c>
       <c r="C80" t="n">
-        <v>0.175</v>
+        <v>0.11875</v>
       </c>
       <c r="D80" t="n">
-        <v>0.6267927650567272</v>
+        <v>0.5899523430683611</v>
       </c>
     </row>
     <row r="81">
@@ -1552,10 +1552,10 @@
         <v>2.70805020110221</v>
       </c>
       <c r="C81" t="n">
-        <v>0.2</v>
+        <v>0.1416666666666667</v>
       </c>
       <c r="D81" t="n">
-        <v>0.6628442448996408</v>
+        <v>0.5995733071765319</v>
       </c>
     </row>
     <row r="82">
@@ -1566,10 +1566,10 @@
         <v>2.70805020110221</v>
       </c>
       <c r="C82" t="n">
-        <v>0.225</v>
+        <v>0.1645833333333333</v>
       </c>
       <c r="D82" t="n">
-        <v>0.6898858525424121</v>
+        <v>0.6097450773331212</v>
       </c>
     </row>
     <row r="83">
@@ -1580,10 +1580,10 @@
         <v>2.70805020110221</v>
       </c>
       <c r="C83" t="n">
-        <v>0.25</v>
+        <v>0.1875</v>
       </c>
       <c r="D83" t="n">
-        <v>0.7094289757721294</v>
+        <v>0.622811999329573</v>
       </c>
     </row>
     <row r="84">
@@ -1594,10 +1594,10 @@
         <v>2.70805020110221</v>
       </c>
       <c r="C84" t="n">
-        <v>0.275</v>
+        <v>0.2104166666666666</v>
       </c>
       <c r="D84" t="n">
-        <v>0.7229850023758799</v>
+        <v>0.6349507136072891</v>
       </c>
     </row>
     <row r="85">
@@ -1608,10 +1608,10 @@
         <v>2.70805020110221</v>
       </c>
       <c r="C85" t="n">
-        <v>0.3</v>
+        <v>0.2333333333333333</v>
       </c>
       <c r="D85" t="n">
-        <v>0.7320653201407521</v>
+        <v>0.6450948925000139</v>
       </c>
     </row>
     <row r="86">
@@ -1622,10 +1622,10 @@
         <v>2.70805020110221</v>
       </c>
       <c r="C86" t="n">
-        <v>0.325</v>
+        <v>0.25625</v>
       </c>
       <c r="D86" t="n">
-        <v>0.738276942703345</v>
+        <v>0.6554064843182891</v>
       </c>
     </row>
     <row r="87">
@@ -1636,10 +1636,10 @@
         <v>2.70805020110221</v>
       </c>
       <c r="C87" t="n">
-        <v>0.35</v>
+        <v>0.2791666666666667</v>
       </c>
       <c r="D87" t="n">
-        <v>0.7436093870983037</v>
+        <v>0.6661816430734191</v>
       </c>
     </row>
     <row r="88">
@@ -1650,10 +1650,10 @@
         <v>2.70805020110221</v>
       </c>
       <c r="C88" t="n">
-        <v>0.375</v>
+        <v>0.3020833333333333</v>
       </c>
       <c r="D88" t="n">
-        <v>0.7501477962097851</v>
+        <v>0.6739958568428822</v>
       </c>
     </row>
     <row r="89">
@@ -1664,10 +1664,10 @@
         <v>2.70805020110221</v>
       </c>
       <c r="C89" t="n">
-        <v>0.4</v>
+        <v>0.325</v>
       </c>
       <c r="D89" t="n">
-        <v>0.7599773129219459</v>
+        <v>0.6767019264208066</v>
       </c>
     </row>
     <row r="90">
@@ -1678,10 +1678,10 @@
         <v>2.70805020110221</v>
       </c>
       <c r="C90" t="n">
-        <v>0.4249999999999999</v>
+        <v>0.3479166666666667</v>
       </c>
       <c r="D90" t="n">
-        <v>0.7742058613995604</v>
+        <v>0.6772591782616579</v>
       </c>
     </row>
     <row r="91">
@@ -1692,10 +1692,10 @@
         <v>2.70805020110221</v>
       </c>
       <c r="C91" t="n">
-        <v>0.45</v>
+        <v>0.3708333333333333</v>
       </c>
       <c r="D91" t="n">
-        <v>0.7900324909298728</v>
+        <v>0.6789591912944377</v>
       </c>
     </row>
     <row r="92">
@@ -1706,10 +1706,10 @@
         <v>2.70805020110221</v>
       </c>
       <c r="C92" t="n">
-        <v>0.475</v>
+        <v>0.39375</v>
       </c>
       <c r="D92" t="n">
-        <v>0.8036790320807449</v>
+        <v>0.6817349990563413</v>
       </c>
     </row>
     <row r="93">
@@ -1720,10 +1720,10 @@
         <v>2.70805020110221</v>
       </c>
       <c r="C93" t="n">
-        <v>0.5</v>
+        <v>0.4166666666666666</v>
       </c>
       <c r="D93" t="n">
-        <v>0.8113673154200383</v>
+        <v>0.6844828402914742</v>
       </c>
     </row>
     <row r="94">
@@ -1734,10 +1734,10 @@
         <v>2.70805020110221</v>
       </c>
       <c r="C94" t="n">
-        <v>0.525</v>
+        <v>0.4395833333333333</v>
       </c>
       <c r="D94" t="n">
-        <v>0.8104112246694049</v>
+        <v>0.6866976379010266</v>
       </c>
     </row>
     <row r="95">
@@ -1748,10 +1748,10 @@
         <v>2.70805020110221</v>
       </c>
       <c r="C95" t="n">
-        <v>0.5499999999999999</v>
+        <v>0.4625</v>
       </c>
       <c r="D95" t="n">
-        <v>0.8024928561656566</v>
+        <v>0.6882270637360679</v>
       </c>
     </row>
     <row r="96">
@@ -1762,10 +1762,10 @@
         <v>2.70805020110221</v>
       </c>
       <c r="C96" t="n">
-        <v>0.575</v>
+        <v>0.4854166666666666</v>
       </c>
       <c r="D96" t="n">
-        <v>0.7903863593993953</v>
+        <v>0.6893790436766513</v>
       </c>
     </row>
     <row r="97">
@@ -1776,10 +1776,10 @@
         <v>2.70805020110221</v>
       </c>
       <c r="C97" t="n">
-        <v>0.6</v>
+        <v>0.5083333333333333</v>
       </c>
       <c r="D97" t="n">
-        <v>0.7768658838612233</v>
+        <v>0.6908544577806247</v>
       </c>
     </row>
     <row r="98">
@@ -1790,10 +1790,10 @@
         <v>2.70805020110221</v>
       </c>
       <c r="C98" t="n">
-        <v>0.6249999999999999</v>
+        <v>0.53125</v>
       </c>
       <c r="D98" t="n">
-        <v>0.7647055790417426</v>
+        <v>0.6927435313439605</v>
       </c>
     </row>
     <row r="99">
@@ -1804,10 +1804,10 @@
         <v>2.70805020110221</v>
       </c>
       <c r="C99" t="n">
-        <v>0.6499999999999999</v>
+        <v>0.5541666666666667</v>
       </c>
       <c r="D99" t="n">
-        <v>0.7566795944315551</v>
+        <v>0.6942431171942028</v>
       </c>
     </row>
     <row r="100">
@@ -1818,10 +1818,10 @@
         <v>2.70805020110221</v>
       </c>
       <c r="C100" t="n">
-        <v>0.6749999999999999</v>
+        <v>0.5770833333333334</v>
       </c>
       <c r="D100" t="n">
-        <v>0.755562079521263</v>
+        <v>0.6944813626080725</v>
       </c>
     </row>
     <row r="101">
@@ -1832,10 +1832,10 @@
         <v>2.70805020110221</v>
       </c>
       <c r="C101" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="D101" t="n">
-        <v>0.764127183801468</v>
+        <v>0.6925864148622903</v>
       </c>
     </row>
     <row r="102">
@@ -1846,10 +1846,10 @@
         <v>-2.302585092994045</v>
       </c>
       <c r="C102" t="n">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="D102" t="n">
-        <v>0.3098438893011644</v>
+        <v>0.3392312701610111</v>
       </c>
     </row>
     <row r="103">
@@ -1860,10 +1860,10 @@
         <v>-2.302585092994045</v>
       </c>
       <c r="C103" t="n">
-        <v>0.125</v>
+        <v>0.07291666666666667</v>
       </c>
       <c r="D103" t="n">
-        <v>0.3285253842559337</v>
+        <v>0.3637286051993103</v>
       </c>
     </row>
     <row r="104">
@@ -1874,10 +1874,10 @@
         <v>-2.302585092994045</v>
       </c>
       <c r="C104" t="n">
-        <v>0.15</v>
+        <v>0.09583333333333333</v>
       </c>
       <c r="D104" t="n">
-        <v>0.3473924082115486</v>
+        <v>0.3805139598143163</v>
       </c>
     </row>
     <row r="105">
@@ -1888,10 +1888,10 @@
         <v>-2.302585092994045</v>
       </c>
       <c r="C105" t="n">
-        <v>0.175</v>
+        <v>0.11875</v>
       </c>
       <c r="D105" t="n">
-        <v>0.3660836647614563</v>
+        <v>0.3931956491314741</v>
       </c>
     </row>
     <row r="106">
@@ -1902,10 +1902,10 @@
         <v>-2.302585092994045</v>
       </c>
       <c r="C106" t="n">
-        <v>0.2</v>
+        <v>0.1416666666666667</v>
       </c>
       <c r="D106" t="n">
-        <v>0.3842378574991041</v>
+        <v>0.4053819882762291</v>
       </c>
     </row>
     <row r="107">
@@ -1916,10 +1916,10 @@
         <v>-2.302585092994045</v>
       </c>
       <c r="C107" t="n">
-        <v>0.225</v>
+        <v>0.1645833333333333</v>
       </c>
       <c r="D107" t="n">
-        <v>0.4014936900179392</v>
+        <v>0.4202094930738269</v>
       </c>
     </row>
     <row r="108">
@@ -1930,10 +1930,10 @@
         <v>-2.302585092994045</v>
       </c>
       <c r="C108" t="n">
-        <v>0.25</v>
+        <v>0.1875</v>
       </c>
       <c r="D108" t="n">
-        <v>0.417489865911409</v>
+        <v>0.4346799129387539</v>
       </c>
     </row>
     <row r="109">
@@ -1944,10 +1944,10 @@
         <v>-2.302585092994045</v>
       </c>
       <c r="C109" t="n">
-        <v>0.275</v>
+        <v>0.2104166666666666</v>
       </c>
       <c r="D109" t="n">
-        <v>0.4318650887729606</v>
+        <v>0.4417812907213957</v>
       </c>
     </row>
     <row r="110">
@@ -1958,10 +1958,10 @@
         <v>-2.302585092994045</v>
       </c>
       <c r="C110" t="n">
-        <v>0.3</v>
+        <v>0.2333333333333333</v>
       </c>
       <c r="D110" t="n">
-        <v>0.4442580621960414</v>
+        <v>0.4423680865303265</v>
       </c>
     </row>
     <row r="111">
@@ -1972,10 +1972,10 @@
         <v>-2.302585092994045</v>
       </c>
       <c r="C111" t="n">
-        <v>0.325</v>
+        <v>0.25625</v>
       </c>
       <c r="D111" t="n">
-        <v>0.4543063638019769</v>
+        <v>0.446167411094751</v>
       </c>
     </row>
     <row r="112">
@@ -1986,10 +1986,10 @@
         <v>-2.302585092994045</v>
       </c>
       <c r="C112" t="n">
-        <v>0.35</v>
+        <v>0.2791666666666667</v>
       </c>
       <c r="D112" t="n">
-        <v>0.4616430673236055</v>
+        <v>0.4551981748144024</v>
       </c>
     </row>
     <row r="113">
@@ -2000,10 +2000,10 @@
         <v>-2.302585092994045</v>
       </c>
       <c r="C113" t="n">
-        <v>0.375</v>
+        <v>0.3020833333333333</v>
       </c>
       <c r="D113" t="n">
-        <v>0.4659001205216439</v>
+        <v>0.4565443360270913</v>
       </c>
     </row>
     <row r="114">
@@ -2014,10 +2014,10 @@
         <v>-2.302585092994045</v>
       </c>
       <c r="C114" t="n">
-        <v>0.4</v>
+        <v>0.325</v>
       </c>
       <c r="D114" t="n">
-        <v>0.4667094711568088</v>
+        <v>0.4450547923093864</v>
       </c>
     </row>
     <row r="115">
@@ -2028,10 +2028,10 @@
         <v>-2.302585092994045</v>
       </c>
       <c r="C115" t="n">
-        <v>0.4249999999999999</v>
+        <v>0.3479166666666667</v>
       </c>
       <c r="D115" t="n">
-        <v>0.4639068469628576</v>
+        <v>0.4441261892262789</v>
       </c>
     </row>
     <row r="116">
@@ -2042,10 +2042,10 @@
         <v>-2.302585092994045</v>
       </c>
       <c r="C116" t="n">
-        <v>0.45</v>
+        <v>0.3708333333333333</v>
       </c>
       <c r="D116" t="n">
-        <v>0.4581430955657096</v>
+        <v>0.473806294002412</v>
       </c>
     </row>
     <row r="117">
@@ -2056,10 +2056,10 @@
         <v>-2.302585092994045</v>
       </c>
       <c r="C117" t="n">
-        <v>0.475</v>
+        <v>0.39375</v>
       </c>
       <c r="D117" t="n">
-        <v>0.4502728445643253</v>
+        <v>0.5079766769254402</v>
       </c>
     </row>
     <row r="118">
@@ -2070,10 +2070,10 @@
         <v>-2.302585092994045</v>
       </c>
       <c r="C118" t="n">
-        <v>0.5</v>
+        <v>0.4166666666666666</v>
       </c>
       <c r="D118" t="n">
-        <v>0.4411507215576645</v>
+        <v>0.5099667680476073</v>
       </c>
     </row>
     <row r="119">
@@ -2084,10 +2084,10 @@
         <v>-2.302585092994045</v>
       </c>
       <c r="C119" t="n">
-        <v>0.525</v>
+        <v>0.4395833333333333</v>
       </c>
       <c r="D119" t="n">
-        <v>0.4317811540763372</v>
+        <v>0.4860979954797334</v>
       </c>
     </row>
     <row r="120">
@@ -2098,10 +2098,10 @@
         <v>-2.302585092994045</v>
       </c>
       <c r="C120" t="n">
-        <v>0.5499999999999999</v>
+        <v>0.4625</v>
       </c>
       <c r="D120" t="n">
-        <v>0.4237677693775515</v>
+        <v>0.4653355266808543</v>
       </c>
     </row>
     <row r="121">
@@ -2112,10 +2112,10 @@
         <v>-2.302585092994045</v>
       </c>
       <c r="C121" t="n">
-        <v>0.575</v>
+        <v>0.4854166666666666</v>
       </c>
       <c r="D121" t="n">
-        <v>0.4188639946501647</v>
+        <v>0.4596989954809029</v>
       </c>
     </row>
     <row r="122">
@@ -2126,10 +2126,10 @@
         <v>-2.302585092994045</v>
       </c>
       <c r="C122" t="n">
-        <v>0.6</v>
+        <v>0.5083333333333333</v>
       </c>
       <c r="D122" t="n">
-        <v>0.4188232570830346</v>
+        <v>0.4659194045985161</v>
       </c>
     </row>
     <row r="123">
@@ -2140,10 +2140,10 @@
         <v>-2.302585092994045</v>
       </c>
       <c r="C123" t="n">
-        <v>0.6249999999999999</v>
+        <v>0.53125</v>
       </c>
       <c r="D123" t="n">
-        <v>0.4253989838650187</v>
+        <v>0.4789969338253364</v>
       </c>
     </row>
     <row r="124">
@@ -2154,10 +2154,10 @@
         <v>-2.302585092994045</v>
       </c>
       <c r="C124" t="n">
-        <v>0.6499999999999999</v>
+        <v>0.5541666666666667</v>
       </c>
       <c r="D124" t="n">
-        <v>0.4403446021849748</v>
+        <v>0.4922154947850341</v>
       </c>
     </row>
     <row r="125">
@@ -2168,10 +2168,10 @@
         <v>-2.302585092994045</v>
       </c>
       <c r="C125" t="n">
-        <v>0.6749999999999999</v>
+        <v>0.5770833333333334</v>
       </c>
       <c r="D125" t="n">
-        <v>0.4654135392317603</v>
+        <v>0.4987270080740112</v>
       </c>
     </row>
     <row r="126">
@@ -2182,10 +2182,10 @@
         <v>-2.302585092994045</v>
       </c>
       <c r="C126" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="D126" t="n">
-        <v>0.5023592221942329</v>
+        <v>0.4916833942886704</v>
       </c>
     </row>
     <row r="127">
@@ -2193,13 +2193,13 @@
         <v>0.0007855459544383347</v>
       </c>
       <c r="B127" t="n">
-        <v>0</v>
+        <v>4.440892098500626e-16</v>
       </c>
       <c r="C127" t="n">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="D127" t="n">
-        <v>0.4556661920116557</v>
+        <v>0.4159306900148736</v>
       </c>
     </row>
     <row r="128">
@@ -2207,13 +2207,13 @@
         <v>0.0007855459544383347</v>
       </c>
       <c r="B128" t="n">
-        <v>0</v>
+        <v>4.440892098500626e-16</v>
       </c>
       <c r="C128" t="n">
-        <v>0.125</v>
+        <v>0.07291666666666667</v>
       </c>
       <c r="D128" t="n">
-        <v>0.4879118876234076</v>
+        <v>0.4614346673650015</v>
       </c>
     </row>
     <row r="129">
@@ -2221,13 +2221,13 @@
         <v>0.0007855459544383347</v>
       </c>
       <c r="B129" t="n">
-        <v>0</v>
+        <v>4.440892098500626e-16</v>
       </c>
       <c r="C129" t="n">
-        <v>0.15</v>
+        <v>0.09583333333333333</v>
       </c>
       <c r="D129" t="n">
-        <v>0.5156009719227209</v>
+        <v>0.4923654941097969</v>
       </c>
     </row>
     <row r="130">
@@ -2235,13 +2235,13 @@
         <v>0.0007855459544383347</v>
       </c>
       <c r="B130" t="n">
-        <v>0</v>
+        <v>4.440892098500626e-16</v>
       </c>
       <c r="C130" t="n">
-        <v>0.175</v>
+        <v>0.11875</v>
       </c>
       <c r="D130" t="n">
-        <v>0.5391437068380706</v>
+        <v>0.5126680183165913</v>
       </c>
     </row>
     <row r="131">
@@ -2249,13 +2249,13 @@
         <v>0.0007855459544383347</v>
       </c>
       <c r="B131" t="n">
-        <v>0</v>
+        <v>4.440892098500626e-16</v>
       </c>
       <c r="C131" t="n">
-        <v>0.2</v>
+        <v>0.1416666666666667</v>
       </c>
       <c r="D131" t="n">
-        <v>0.5589503542979322</v>
+        <v>0.5262870880527166</v>
       </c>
     </row>
     <row r="132">
@@ -2263,13 +2263,13 @@
         <v>0.0007855459544383347</v>
       </c>
       <c r="B132" t="n">
-        <v>0</v>
+        <v>4.440892098500626e-16</v>
       </c>
       <c r="C132" t="n">
-        <v>0.225</v>
+        <v>0.1645833333333333</v>
       </c>
       <c r="D132" t="n">
-        <v>0.575431176230781</v>
+        <v>0.5370235614581853</v>
       </c>
     </row>
     <row r="133">
@@ -2277,13 +2277,13 @@
         <v>0.0007855459544383347</v>
       </c>
       <c r="B133" t="n">
-        <v>0</v>
+        <v>4.440892098500626e-16</v>
       </c>
       <c r="C133" t="n">
-        <v>0.25</v>
+        <v>0.1875</v>
       </c>
       <c r="D133" t="n">
-        <v>0.5889964345650922</v>
+        <v>0.5468060078221558</v>
       </c>
     </row>
     <row r="134">
@@ -2291,13 +2291,13 @@
         <v>0.0007855459544383347</v>
       </c>
       <c r="B134" t="n">
-        <v>0</v>
+        <v>4.440892098500626e-16</v>
       </c>
       <c r="C134" t="n">
-        <v>0.275</v>
+        <v>0.2104166666666666</v>
       </c>
       <c r="D134" t="n">
-        <v>0.6000563912293411</v>
+        <v>0.5562335190054395</v>
       </c>
     </row>
     <row r="135">
@@ -2305,13 +2305,13 @@
         <v>0.0007855459544383347</v>
       </c>
       <c r="B135" t="n">
-        <v>0</v>
+        <v>4.440892098500626e-16</v>
       </c>
       <c r="C135" t="n">
-        <v>0.3</v>
+        <v>0.2333333333333333</v>
       </c>
       <c r="D135" t="n">
-        <v>0.6090213081520034</v>
+        <v>0.5652990871992667</v>
       </c>
     </row>
     <row r="136">
@@ -2319,13 +2319,13 @@
         <v>0.0007855459544383347</v>
       </c>
       <c r="B136" t="n">
-        <v>0</v>
+        <v>4.440892098500626e-16</v>
       </c>
       <c r="C136" t="n">
-        <v>0.325</v>
+        <v>0.25625</v>
       </c>
       <c r="D136" t="n">
-        <v>0.6162663056116012</v>
+        <v>0.5733448682711806</v>
       </c>
     </row>
     <row r="137">
@@ -2333,13 +2333,13 @@
         <v>0.0007855459544383347</v>
       </c>
       <c r="B137" t="n">
-        <v>0</v>
+        <v>4.440892098500626e-16</v>
       </c>
       <c r="C137" t="n">
-        <v>0.35</v>
+        <v>0.2791666666666667</v>
       </c>
       <c r="D137" t="n">
-        <v>0.6220259372868457</v>
+        <v>0.5798114199176425</v>
       </c>
     </row>
     <row r="138">
@@ -2347,13 +2347,13 @@
         <v>0.0007855459544383347</v>
       </c>
       <c r="B138" t="n">
-        <v>0</v>
+        <v>4.440892098500626e-16</v>
       </c>
       <c r="C138" t="n">
-        <v>0.375</v>
+        <v>0.3020833333333333</v>
       </c>
       <c r="D138" t="n">
-        <v>0.6264996152064949</v>
+        <v>0.5843833208510453</v>
       </c>
     </row>
     <row r="139">
@@ -2361,13 +2361,13 @@
         <v>0.0007855459544383347</v>
       </c>
       <c r="B139" t="n">
-        <v>0</v>
+        <v>4.440892098500626e-16</v>
       </c>
       <c r="C139" t="n">
-        <v>0.4</v>
+        <v>0.325</v>
       </c>
       <c r="D139" t="n">
-        <v>0.6298867513993071</v>
+        <v>0.5883674140144322</v>
       </c>
     </row>
     <row r="140">
@@ -2375,13 +2375,13 @@
         <v>0.0007855459544383347</v>
       </c>
       <c r="B140" t="n">
-        <v>0</v>
+        <v>4.440892098500626e-16</v>
       </c>
       <c r="C140" t="n">
-        <v>0.4249999999999999</v>
+        <v>0.3479166666666667</v>
       </c>
       <c r="D140" t="n">
-        <v>0.6323578009504219</v>
+        <v>0.597942134913433</v>
       </c>
     </row>
     <row r="141">
@@ -2389,13 +2389,13 @@
         <v>0.0007855459544383347</v>
       </c>
       <c r="B141" t="n">
-        <v>0</v>
+        <v>4.440892098500626e-16</v>
       </c>
       <c r="C141" t="n">
-        <v>0.45</v>
+        <v>0.3708333333333333</v>
       </c>
       <c r="D141" t="n">
-        <v>0.6339673911705065</v>
+        <v>0.617178321595752</v>
       </c>
     </row>
     <row r="142">
@@ -2403,13 +2403,13 @@
         <v>0.0007855459544383347</v>
       </c>
       <c r="B142" t="n">
-        <v>0</v>
+        <v>4.440892098500626e-16</v>
       </c>
       <c r="C142" t="n">
-        <v>0.475</v>
+        <v>0.39375</v>
       </c>
       <c r="D142" t="n">
-        <v>0.6347411924266093</v>
+        <v>0.6341871493203636</v>
       </c>
     </row>
     <row r="143">
@@ -2417,13 +2417,13 @@
         <v>0.0007855459544383347</v>
       </c>
       <c r="B143" t="n">
-        <v>0</v>
+        <v>4.440892098500626e-16</v>
       </c>
       <c r="C143" t="n">
-        <v>0.5</v>
+        <v>0.4166666666666666</v>
       </c>
       <c r="D143" t="n">
-        <v>0.6347048750857791</v>
+        <v>0.6340473311671294</v>
       </c>
     </row>
     <row r="144">
@@ -2431,13 +2431,13 @@
         <v>0.0007855459544383347</v>
       </c>
       <c r="B144" t="n">
-        <v>0</v>
+        <v>4.440892098500626e-16</v>
       </c>
       <c r="C144" t="n">
-        <v>0.525</v>
+        <v>0.4395833333333333</v>
       </c>
       <c r="D144" t="n">
-        <v>0.6340202132385782</v>
+        <v>0.6224826559618186</v>
       </c>
     </row>
     <row r="145">
@@ -2445,13 +2445,13 @@
         <v>0.0007855459544383347</v>
       </c>
       <c r="B145" t="n">
-        <v>0</v>
+        <v>4.440892098500626e-16</v>
       </c>
       <c r="C145" t="n">
-        <v>0.5499999999999999</v>
+        <v>0.4625</v>
       </c>
       <c r="D145" t="n">
-        <v>0.6333933958696235</v>
+        <v>0.6158694773129723</v>
       </c>
     </row>
     <row r="146">
@@ -2459,13 +2459,13 @@
         <v>0.0007855459544383347</v>
       </c>
       <c r="B146" t="n">
-        <v>0</v>
+        <v>4.440892098500626e-16</v>
       </c>
       <c r="C146" t="n">
-        <v>0.575</v>
+        <v>0.4854166666666666</v>
       </c>
       <c r="D146" t="n">
-        <v>0.633666715687046</v>
+        <v>0.6183137964542235</v>
       </c>
     </row>
     <row r="147">
@@ -2473,13 +2473,13 @@
         <v>0.0007855459544383347</v>
       </c>
       <c r="B147" t="n">
-        <v>0</v>
+        <v>4.440892098500626e-16</v>
       </c>
       <c r="C147" t="n">
-        <v>0.6</v>
+        <v>0.5083333333333333</v>
       </c>
       <c r="D147" t="n">
-        <v>0.6356824653989764</v>
+        <v>0.6229859679408478</v>
       </c>
     </row>
     <row r="148">
@@ -2487,13 +2487,13 @@
         <v>0.0007855459544383347</v>
       </c>
       <c r="B148" t="n">
-        <v>0</v>
+        <v>4.440892098500626e-16</v>
       </c>
       <c r="C148" t="n">
-        <v>0.6249999999999999</v>
+        <v>0.53125</v>
       </c>
       <c r="D148" t="n">
-        <v>0.6402829377135456</v>
+        <v>0.6258329499678748</v>
       </c>
     </row>
     <row r="149">
@@ -2501,13 +2501,13 @@
         <v>0.0007855459544383347</v>
       </c>
       <c r="B149" t="n">
-        <v>0</v>
+        <v>4.440892098500626e-16</v>
       </c>
       <c r="C149" t="n">
-        <v>0.6499999999999999</v>
+        <v>0.5541666666666667</v>
       </c>
       <c r="D149" t="n">
-        <v>0.6483104253388841</v>
+        <v>0.6273188830786558</v>
       </c>
     </row>
     <row r="150">
@@ -2515,13 +2515,13 @@
         <v>0.0007855459544383347</v>
       </c>
       <c r="B150" t="n">
-        <v>0</v>
+        <v>4.440892098500626e-16</v>
       </c>
       <c r="C150" t="n">
-        <v>0.6749999999999999</v>
+        <v>0.5770833333333334</v>
       </c>
       <c r="D150" t="n">
-        <v>0.6606072209831229</v>
+        <v>0.6282553054724785</v>
       </c>
     </row>
     <row r="151">
@@ -2529,13 +2529,13 @@
         <v>0.0007855459544383347</v>
       </c>
       <c r="B151" t="n">
-        <v>0</v>
+        <v>4.440892098500626e-16</v>
       </c>
       <c r="C151" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="D151" t="n">
-        <v>0.6780156173543928</v>
+        <v>0.6294537553486306</v>
       </c>
     </row>
     <row r="152">
@@ -2546,10 +2546,10 @@
         <v>2.302585092994046</v>
       </c>
       <c r="C152" t="n">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="D152" t="n">
-        <v>0.5521925866882574</v>
+        <v>0.4901807976965654</v>
       </c>
     </row>
     <row r="153">
@@ -2560,10 +2560,10 @@
         <v>2.302585092994046</v>
       </c>
       <c r="C153" t="n">
-        <v>0.125</v>
+        <v>0.07291666666666667</v>
       </c>
       <c r="D153" t="n">
-        <v>0.6042436467042452</v>
+        <v>0.5576996208708259</v>
       </c>
     </row>
     <row r="154">
@@ -2574,10 +2574,10 @@
         <v>2.302585092994046</v>
       </c>
       <c r="C154" t="n">
-        <v>0.15</v>
+        <v>0.09583333333333333</v>
       </c>
       <c r="D154" t="n">
-        <v>0.6490292730620661</v>
+        <v>0.6031290882229987</v>
       </c>
     </row>
     <row r="155">
@@ -2588,10 +2588,10 @@
         <v>2.302585092994046</v>
       </c>
       <c r="C155" t="n">
-        <v>0.175</v>
+        <v>0.11875</v>
       </c>
       <c r="D155" t="n">
-        <v>0.6871582215476071</v>
+        <v>0.6334861766121134</v>
       </c>
     </row>
     <row r="156">
@@ -2602,10 +2602,10 @@
         <v>2.302585092994046</v>
       </c>
       <c r="C156" t="n">
-        <v>0.2</v>
+        <v>0.1416666666666667</v>
       </c>
       <c r="D156" t="n">
-        <v>0.7192392479467548</v>
+        <v>0.6557878628972005</v>
       </c>
     </row>
     <row r="157">
@@ -2616,10 +2616,10 @@
         <v>2.302585092994046</v>
       </c>
       <c r="C157" t="n">
-        <v>0.225</v>
+        <v>0.1645833333333333</v>
       </c>
       <c r="D157" t="n">
-        <v>0.7458811080453958</v>
+        <v>0.6764398828994062</v>
       </c>
     </row>
     <row r="158">
@@ -2630,10 +2630,10 @@
         <v>2.302585092994046</v>
       </c>
       <c r="C158" t="n">
-        <v>0.25</v>
+        <v>0.1875</v>
       </c>
       <c r="D158" t="n">
-        <v>0.7676925576294166</v>
+        <v>0.6939000569035445</v>
       </c>
     </row>
     <row r="159">
@@ -2644,10 +2644,10 @@
         <v>2.302585092994046</v>
       </c>
       <c r="C159" t="n">
-        <v>0.275</v>
+        <v>0.2104166666666666</v>
       </c>
       <c r="D159" t="n">
-        <v>0.785282352484704</v>
+        <v>0.7013979664337023</v>
       </c>
     </row>
     <row r="160">
@@ -2658,10 +2658,10 @@
         <v>2.302585092994046</v>
       </c>
       <c r="C160" t="n">
-        <v>0.3</v>
+        <v>0.2333333333333333</v>
       </c>
       <c r="D160" t="n">
-        <v>0.7992592483971447</v>
+        <v>0.701541315932131</v>
       </c>
     </row>
     <row r="161">
@@ -2672,10 +2672,10 @@
         <v>2.302585092994046</v>
       </c>
       <c r="C161" t="n">
-        <v>0.325</v>
+        <v>0.25625</v>
       </c>
       <c r="D161" t="n">
-        <v>0.8102420390320756</v>
+        <v>0.7075342538482103</v>
       </c>
     </row>
     <row r="162">
@@ -2686,10 +2686,10 @@
         <v>2.302585092994046</v>
       </c>
       <c r="C162" t="n">
-        <v>0.35</v>
+        <v>0.2791666666666667</v>
       </c>
       <c r="D162" t="n">
-        <v>0.8188896695726349</v>
+        <v>0.724218938231812</v>
       </c>
     </row>
     <row r="163">
@@ -2700,10 +2700,10 @@
         <v>2.302585092994046</v>
       </c>
       <c r="C163" t="n">
-        <v>0.375</v>
+        <v>0.3020833333333333</v>
       </c>
       <c r="D163" t="n">
-        <v>0.8258711230814112</v>
+        <v>0.7401378775145727</v>
       </c>
     </row>
     <row r="164">
@@ -2714,10 +2714,10 @@
         <v>2.302585092994046</v>
       </c>
       <c r="C164" t="n">
-        <v>0.4</v>
+        <v>0.325</v>
       </c>
       <c r="D164" t="n">
-        <v>0.8318553826209929</v>
+        <v>0.7464924536584646</v>
       </c>
     </row>
     <row r="165">
@@ -2728,10 +2728,10 @@
         <v>2.302585092994046</v>
       </c>
       <c r="C165" t="n">
-        <v>0.4249999999999999</v>
+        <v>0.3479166666666667</v>
       </c>
       <c r="D165" t="n">
-        <v>0.8373376943656493</v>
+        <v>0.7478922710776925</v>
       </c>
     </row>
     <row r="166">
@@ -2742,10 +2742,10 @@
         <v>2.302585092994046</v>
       </c>
       <c r="C166" t="n">
-        <v>0.45</v>
+        <v>0.3708333333333333</v>
       </c>
       <c r="D166" t="n">
-        <v>0.8421183569363723</v>
+        <v>0.7503753271551142</v>
       </c>
     </row>
     <row r="167">
@@ -2756,10 +2756,10 @@
         <v>2.302585092994046</v>
       </c>
       <c r="C167" t="n">
-        <v>0.475</v>
+        <v>0.39375</v>
       </c>
       <c r="D167" t="n">
-        <v>0.8458239320658346</v>
+        <v>0.7540861722294391</v>
       </c>
     </row>
     <row r="168">
@@ -2770,10 +2770,10 @@
         <v>2.302585092994046</v>
       </c>
       <c r="C168" t="n">
-        <v>0.5</v>
+        <v>0.4166666666666666</v>
       </c>
       <c r="D168" t="n">
-        <v>0.8480809814867089</v>
+        <v>0.757367870115586</v>
       </c>
     </row>
     <row r="169">
@@ -2784,10 +2784,10 @@
         <v>2.302585092994046</v>
       </c>
       <c r="C169" t="n">
-        <v>0.525</v>
+        <v>0.4395833333333333</v>
       </c>
       <c r="D169" t="n">
-        <v>0.8486485303363022</v>
+        <v>0.7597816785577097</v>
       </c>
     </row>
     <row r="170">
@@ -2798,10 +2798,10 @@
         <v>2.302585092994046</v>
       </c>
       <c r="C170" t="n">
-        <v>0.5499999999999999</v>
+        <v>0.4625</v>
       </c>
       <c r="D170" t="n">
-        <v>0.8478154573704598</v>
+        <v>0.7615541349104519</v>
       </c>
     </row>
     <row r="171">
@@ -2812,10 +2812,10 @@
         <v>2.302585092994046</v>
       </c>
       <c r="C171" t="n">
-        <v>0.575</v>
+        <v>0.4854166666666666</v>
       </c>
       <c r="D171" t="n">
-        <v>0.8460031047496617</v>
+        <v>0.7628662061859036</v>
       </c>
     </row>
     <row r="172">
@@ -2826,10 +2826,10 @@
         <v>2.302585092994046</v>
       </c>
       <c r="C172" t="n">
-        <v>0.6</v>
+        <v>0.5083333333333333</v>
       </c>
       <c r="D172" t="n">
-        <v>0.8436328146343873</v>
+        <v>0.7638502019341313</v>
       </c>
     </row>
     <row r="173">
@@ -2840,10 +2840,10 @@
         <v>2.302585092994046</v>
       </c>
       <c r="C173" t="n">
-        <v>0.6249999999999999</v>
+        <v>0.53125</v>
       </c>
       <c r="D173" t="n">
-        <v>0.8411259291851165</v>
+        <v>0.76453407511195</v>
       </c>
     </row>
     <row r="174">
@@ -2854,10 +2854,10 @@
         <v>2.302585092994046</v>
       </c>
       <c r="C174" t="n">
-        <v>0.6499999999999999</v>
+        <v>0.5541666666666667</v>
       </c>
       <c r="D174" t="n">
-        <v>0.8389037905623293</v>
+        <v>0.7647988682220567</v>
       </c>
     </row>
     <row r="175">
@@ -2868,10 +2868,10 @@
         <v>2.302585092994046</v>
       </c>
       <c r="C175" t="n">
-        <v>0.6749999999999999</v>
+        <v>0.5770833333333334</v>
       </c>
       <c r="D175" t="n">
-        <v>0.8373877409265053</v>
+        <v>0.7645143254967981</v>
       </c>
     </row>
     <row r="176">
@@ -2882,10 +2882,10 @@
         <v>2.302585092994046</v>
       </c>
       <c r="C176" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="D176" t="n">
-        <v>0.8369991224381241</v>
+        <v>0.7635501911685212</v>
       </c>
     </row>
     <row r="177">
@@ -2896,10 +2896,10 @@
         <v>2.70805020110221</v>
       </c>
       <c r="C177" t="n">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="D177" t="n">
-        <v>0.5906330962153115</v>
+        <v>0.5141138799814953</v>
       </c>
     </row>
     <row r="178">
@@ -2910,10 +2910,10 @@
         <v>2.70805020110221</v>
       </c>
       <c r="C178" t="n">
-        <v>0.125</v>
+        <v>0.07291666666666667</v>
       </c>
       <c r="D178" t="n">
-        <v>0.64659146916301</v>
+        <v>0.5740988540225023</v>
       </c>
     </row>
     <row r="179">
@@ -2924,10 +2924,10 @@
         <v>2.70805020110221</v>
       </c>
       <c r="C179" t="n">
-        <v>0.15</v>
+        <v>0.09583333333333333</v>
       </c>
       <c r="D179" t="n">
-        <v>0.6955022244333449</v>
+        <v>0.6188550946906253</v>
       </c>
     </row>
     <row r="180">
@@ -2938,10 +2938,10 @@
         <v>2.70805020110221</v>
       </c>
       <c r="C180" t="n">
-        <v>0.175</v>
+        <v>0.11875</v>
       </c>
       <c r="D180" t="n">
-        <v>0.7376395424665083</v>
+        <v>0.6523766211400054</v>
       </c>
     </row>
     <row r="181">
@@ -2952,10 +2952,10 @@
         <v>2.70805020110221</v>
       </c>
       <c r="C181" t="n">
-        <v>0.2</v>
+        <v>0.1416666666666667</v>
       </c>
       <c r="D181" t="n">
-        <v>0.7732776037026932</v>
+        <v>0.6786574525247839</v>
       </c>
     </row>
     <row r="182">
@@ -2966,10 +2966,10 @@
         <v>2.70805020110221</v>
       </c>
       <c r="C182" t="n">
-        <v>0.225</v>
+        <v>0.1645833333333333</v>
       </c>
       <c r="D182" t="n">
-        <v>0.8026905885820916</v>
+        <v>0.7013034766828088</v>
       </c>
     </row>
     <row r="183">
@@ -2980,10 +2980,10 @@
         <v>2.70805020110221</v>
       </c>
       <c r="C183" t="n">
-        <v>0.25</v>
+        <v>0.1875</v>
       </c>
       <c r="D183" t="n">
-        <v>0.8261526775448964</v>
+        <v>0.71887374276194</v>
       </c>
     </row>
     <row r="184">
@@ -2994,10 +2994,10 @@
         <v>2.70805020110221</v>
       </c>
       <c r="C184" t="n">
-        <v>0.275</v>
+        <v>0.2104166666666666</v>
       </c>
       <c r="D184" t="n">
-        <v>0.8439380510313</v>
+        <v>0.7266820920407678</v>
       </c>
     </row>
     <row r="185">
@@ -3008,10 +3008,10 @@
         <v>2.70805020110221</v>
       </c>
       <c r="C185" t="n">
-        <v>0.3</v>
+        <v>0.2333333333333333</v>
       </c>
       <c r="D185" t="n">
-        <v>0.8563208894814949</v>
+        <v>0.7281453638912452</v>
       </c>
     </row>
     <row r="186">
@@ -3022,10 +3022,10 @@
         <v>2.70805020110221</v>
       </c>
       <c r="C186" t="n">
-        <v>0.325</v>
+        <v>0.25625</v>
       </c>
       <c r="D186" t="n">
-        <v>0.8638731166424328</v>
+        <v>0.7357991105357543</v>
       </c>
     </row>
     <row r="187">
@@ -3036,10 +3036,10 @@
         <v>2.70805020110221</v>
       </c>
       <c r="C187" t="n">
-        <v>0.35</v>
+        <v>0.2791666666666667</v>
       </c>
       <c r="D187" t="n">
-        <v>0.8683576294881028</v>
+        <v>0.7542161273315856</v>
       </c>
     </row>
     <row r="188">
@@ -3050,10 +3050,10 @@
         <v>2.70805020110221</v>
       </c>
       <c r="C188" t="n">
-        <v>0.375</v>
+        <v>0.3020833333333333</v>
       </c>
       <c r="D188" t="n">
-        <v>0.8718350682992529</v>
+        <v>0.7725419732371687</v>
       </c>
     </row>
     <row r="189">
@@ -3064,10 +3064,10 @@
         <v>2.70805020110221</v>
       </c>
       <c r="C189" t="n">
-        <v>0.4</v>
+        <v>0.325</v>
       </c>
       <c r="D189" t="n">
-        <v>0.8763660733566314</v>
+        <v>0.7816612521325109</v>
       </c>
     </row>
     <row r="190">
@@ -3078,10 +3078,10 @@
         <v>2.70805020110221</v>
       </c>
       <c r="C190" t="n">
-        <v>0.4249999999999999</v>
+        <v>0.3479166666666667</v>
       </c>
       <c r="D190" t="n">
-        <v>0.883344110140893</v>
+        <v>0.782776301448514</v>
       </c>
     </row>
     <row r="191">
@@ -3092,10 +3092,10 @@
         <v>2.70805020110221</v>
       </c>
       <c r="C191" t="n">
-        <v>0.45</v>
+        <v>0.3708333333333333</v>
       </c>
       <c r="D191" t="n">
-        <v>0.8914939449323189</v>
+        <v>0.7795577671932419</v>
       </c>
     </row>
     <row r="192">
@@ -3106,10 +3106,10 @@
         <v>2.70805020110221</v>
       </c>
       <c r="C192" t="n">
-        <v>0.475</v>
+        <v>0.39375</v>
       </c>
       <c r="D192" t="n">
-        <v>0.8988731692110972</v>
+        <v>0.7783443332483218</v>
       </c>
     </row>
     <row r="193">
@@ -3120,10 +3120,10 @@
         <v>2.70805020110221</v>
       </c>
       <c r="C193" t="n">
-        <v>0.5</v>
+        <v>0.4166666666666666</v>
       </c>
       <c r="D193" t="n">
-        <v>0.9035393744574156</v>
+        <v>0.7851283305840623</v>
       </c>
     </row>
     <row r="194">
@@ -3134,10 +3134,10 @@
         <v>2.70805020110221</v>
       </c>
       <c r="C194" t="n">
-        <v>0.525</v>
+        <v>0.4395833333333333</v>
       </c>
       <c r="D194" t="n">
-        <v>0.904048912807329</v>
+        <v>0.7944327423777464</v>
       </c>
     </row>
     <row r="195">
@@ -3148,10 +3148,10 @@
         <v>2.70805020110221</v>
       </c>
       <c r="C195" t="n">
-        <v>0.5499999999999999</v>
+        <v>0.4625</v>
       </c>
       <c r="D195" t="n">
-        <v>0.9009531790203597</v>
+        <v>0.7950779254677668</v>
       </c>
     </row>
     <row r="196">
@@ -3162,10 +3162,10 @@
         <v>2.70805020110221</v>
       </c>
       <c r="C196" t="n">
-        <v>0.575</v>
+        <v>0.4854166666666666</v>
       </c>
       <c r="D196" t="n">
-        <v>0.8953023285118969</v>
+        <v>0.7867265558129125</v>
       </c>
     </row>
     <row r="197">
@@ -3176,10 +3176,10 @@
         <v>2.70805020110221</v>
       </c>
       <c r="C197" t="n">
-        <v>0.6</v>
+        <v>0.5083333333333333</v>
       </c>
       <c r="D197" t="n">
-        <v>0.8881465166973299</v>
+        <v>0.7786286847291893</v>
       </c>
     </row>
     <row r="198">
@@ -3190,10 +3190,10 @@
         <v>2.70805020110221</v>
       </c>
       <c r="C198" t="n">
-        <v>0.6249999999999999</v>
+        <v>0.53125</v>
       </c>
       <c r="D198" t="n">
-        <v>0.8805358989920483</v>
+        <v>0.7755424970111756</v>
       </c>
     </row>
     <row r="199">
@@ -3204,10 +3204,10 @@
         <v>2.70805020110221</v>
       </c>
       <c r="C199" t="n">
-        <v>0.6499999999999999</v>
+        <v>0.5541666666666667</v>
       </c>
       <c r="D199" t="n">
-        <v>0.8735206308114409</v>
+        <v>0.7753215771250616</v>
       </c>
     </row>
     <row r="200">
@@ -3218,10 +3218,10 @@
         <v>2.70805020110221</v>
       </c>
       <c r="C200" t="n">
-        <v>0.6749999999999999</v>
+        <v>0.5770833333333334</v>
       </c>
       <c r="D200" t="n">
-        <v>0.8681508675708974</v>
+        <v>0.7752885055207511</v>
       </c>
     </row>
     <row r="201">
@@ -3232,10 +3232,10 @@
         <v>2.70805020110221</v>
       </c>
       <c r="C201" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="D201" t="n">
-        <v>0.8654767646858068</v>
+        <v>0.7727658626481485</v>
       </c>
     </row>
     <row r="202">
@@ -3246,10 +3246,10 @@
         <v>-2.302585092994045</v>
       </c>
       <c r="C202" t="n">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="D202" t="n">
-        <v>0.3759903993648456</v>
+        <v>0.4003835157404837</v>
       </c>
     </row>
     <row r="203">
@@ -3260,10 +3260,10 @@
         <v>-2.302585092994045</v>
       </c>
       <c r="C203" t="n">
-        <v>0.125</v>
+        <v>0.07291666666666667</v>
       </c>
       <c r="D203" t="n">
-        <v>0.4123693986973184</v>
+        <v>0.4261399459263303</v>
       </c>
     </row>
     <row r="204">
@@ -3274,10 +3274,10 @@
         <v>-2.302585092994045</v>
       </c>
       <c r="C204" t="n">
-        <v>0.15</v>
+        <v>0.09583333333333333</v>
       </c>
       <c r="D204" t="n">
-        <v>0.4438501190149184</v>
+        <v>0.4409037916499319</v>
       </c>
     </row>
     <row r="205">
@@ -3288,10 +3288,10 @@
         <v>-2.302585092994045</v>
       </c>
       <c r="C205" t="n">
-        <v>0.175</v>
+        <v>0.11875</v>
       </c>
       <c r="D205" t="n">
-        <v>0.4708377949651401</v>
+        <v>0.452793674888733</v>
       </c>
     </row>
     <row r="206">
@@ -3302,10 +3302,10 @@
         <v>-2.302585092994045</v>
       </c>
       <c r="C206" t="n">
-        <v>0.2</v>
+        <v>0.1416666666666667</v>
       </c>
       <c r="D206" t="n">
-        <v>0.4937376611954777</v>
+        <v>0.4699282176201778</v>
       </c>
     </row>
     <row r="207">
@@ -3316,10 +3316,10 @@
         <v>-2.302585092994045</v>
       </c>
       <c r="C207" t="n">
-        <v>0.225</v>
+        <v>0.1645833333333333</v>
       </c>
       <c r="D207" t="n">
-        <v>0.5129549523534257</v>
+        <v>0.4991171599462367</v>
       </c>
     </row>
     <row r="208">
@@ -3330,10 +3330,10 @@
         <v>-2.302585092994045</v>
       </c>
       <c r="C208" t="n">
-        <v>0.25</v>
+        <v>0.1875</v>
       </c>
       <c r="D208" t="n">
-        <v>0.5288949030864784</v>
+        <v>0.5301509616055718</v>
       </c>
     </row>
     <row r="209">
@@ -3344,10 +3344,10 @@
         <v>-2.302585092994045</v>
       </c>
       <c r="C209" t="n">
-        <v>0.275</v>
+        <v>0.2104166666666666</v>
       </c>
       <c r="D209" t="n">
-        <v>0.54196274804213</v>
+        <v>0.541706865040067</v>
       </c>
     </row>
     <row r="210">
@@ -3358,10 +3358,10 @@
         <v>-2.302585092994045</v>
       </c>
       <c r="C210" t="n">
-        <v>0.3</v>
+        <v>0.2333333333333333</v>
       </c>
       <c r="D210" t="n">
-        <v>0.5525637218678748</v>
+        <v>0.5349109803618173</v>
       </c>
     </row>
     <row r="211">
@@ -3372,10 +3372,10 @@
         <v>-2.302585092994045</v>
       </c>
       <c r="C211" t="n">
-        <v>0.325</v>
+        <v>0.25625</v>
       </c>
       <c r="D211" t="n">
-        <v>0.5610803913309492</v>
+        <v>0.5362477336540851</v>
       </c>
     </row>
     <row r="212">
@@ -3386,10 +3386,10 @@
         <v>-2.302585092994045</v>
       </c>
       <c r="C212" t="n">
-        <v>0.35</v>
+        <v>0.2791666666666667</v>
       </c>
       <c r="D212" t="n">
-        <v>0.5678046516775574</v>
+        <v>0.5546734991944704</v>
       </c>
     </row>
     <row r="213">
@@ -3400,10 +3400,10 @@
         <v>-2.302585092994045</v>
       </c>
       <c r="C213" t="n">
-        <v>0.375</v>
+        <v>0.3020833333333333</v>
       </c>
       <c r="D213" t="n">
-        <v>0.573005730273645</v>
+        <v>0.5646740021060838</v>
       </c>
     </row>
     <row r="214">
@@ -3414,10 +3414,10 @@
         <v>-2.302585092994045</v>
       </c>
       <c r="C214" t="n">
-        <v>0.4</v>
+        <v>0.325</v>
       </c>
       <c r="D214" t="n">
-        <v>0.5769528544851581</v>
+        <v>0.5506039773201213</v>
       </c>
     </row>
     <row r="215">
@@ -3428,10 +3428,10 @@
         <v>-2.302585092994045</v>
       </c>
       <c r="C215" t="n">
-        <v>0.4249999999999999</v>
+        <v>0.3479166666666667</v>
       </c>
       <c r="D215" t="n">
-        <v>0.5799018019205299</v>
+        <v>0.5381319867732474</v>
       </c>
     </row>
     <row r="216">
@@ -3442,10 +3442,10 @@
         <v>-2.302585092994045</v>
       </c>
       <c r="C216" t="n">
-        <v>0.45</v>
+        <v>0.3708333333333333</v>
       </c>
       <c r="D216" t="n">
-        <v>0.5820545511581428</v>
+        <v>0.5532985111453492</v>
       </c>
     </row>
     <row r="217">
@@ -3456,10 +3456,10 @@
         <v>-2.302585092994045</v>
       </c>
       <c r="C217" t="n">
-        <v>0.475</v>
+        <v>0.39375</v>
       </c>
       <c r="D217" t="n">
-        <v>0.5835996310188662</v>
+        <v>0.5827868686189459</v>
       </c>
     </row>
     <row r="218">
@@ -3470,10 +3470,10 @@
         <v>-2.302585092994045</v>
       </c>
       <c r="C218" t="n">
-        <v>0.5</v>
+        <v>0.4166666666666666</v>
       </c>
       <c r="D218" t="n">
-        <v>0.5847255703235702</v>
+        <v>0.6026724677720011</v>
       </c>
     </row>
     <row r="219">
@@ -3484,10 +3484,10 @@
         <v>-2.302585092994045</v>
       </c>
       <c r="C219" t="n">
-        <v>0.525</v>
+        <v>0.4395833333333333</v>
       </c>
       <c r="D219" t="n">
-        <v>0.5856014946708071</v>
+        <v>0.6105337656545823</v>
       </c>
     </row>
     <row r="220">
@@ -3498,10 +3498,10 @@
         <v>-2.302585092994045</v>
       </c>
       <c r="C220" t="n">
-        <v>0.5499999999999999</v>
+        <v>0.4625</v>
       </c>
       <c r="D220" t="n">
-        <v>0.5863189167698624</v>
+        <v>0.6151954198727438</v>
       </c>
     </row>
     <row r="221">
@@ -3512,10 +3512,10 @@
         <v>-2.302585092994045</v>
       </c>
       <c r="C221" t="n">
-        <v>0.575</v>
+        <v>0.4854166666666666</v>
       </c>
       <c r="D221" t="n">
-        <v>0.5869499461077038</v>
+        <v>0.6154867580451524</v>
       </c>
     </row>
     <row r="222">
@@ -3526,10 +3526,10 @@
         <v>-2.302585092994045</v>
       </c>
       <c r="C222" t="n">
-        <v>0.6</v>
+        <v>0.5083333333333333</v>
       </c>
       <c r="D222" t="n">
-        <v>0.5875666921712996</v>
+        <v>0.6014931852546963</v>
       </c>
     </row>
     <row r="223">
@@ -3540,10 +3540,10 @@
         <v>-2.302585092994045</v>
       </c>
       <c r="C223" t="n">
-        <v>0.6249999999999999</v>
+        <v>0.53125</v>
       </c>
       <c r="D223" t="n">
-        <v>0.5882412644476182</v>
+        <v>0.5747010710517317</v>
       </c>
     </row>
     <row r="224">
@@ -3554,10 +3554,10 @@
         <v>-2.302585092994045</v>
       </c>
       <c r="C224" t="n">
-        <v>0.6499999999999999</v>
+        <v>0.5541666666666667</v>
       </c>
       <c r="D224" t="n">
-        <v>0.5890457724236273</v>
+        <v>0.5533461160043175</v>
       </c>
     </row>
     <row r="225">
@@ -3568,10 +3568,10 @@
         <v>-2.302585092994045</v>
       </c>
       <c r="C225" t="n">
-        <v>0.6749999999999999</v>
+        <v>0.5770833333333334</v>
       </c>
       <c r="D225" t="n">
-        <v>0.5900523255862956</v>
+        <v>0.5569521418776148</v>
       </c>
     </row>
     <row r="226">
@@ -3582,10 +3582,10 @@
         <v>-2.302585092994045</v>
       </c>
       <c r="C226" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="D226" t="n">
-        <v>0.5913330334225908</v>
+        <v>0.6050429704367835</v>
       </c>
     </row>
     <row r="227">
@@ -3593,13 +3593,13 @@
         <v>0.0008176614881439084</v>
       </c>
       <c r="B227" t="n">
-        <v>0</v>
+        <v>4.440892098500626e-16</v>
       </c>
       <c r="C227" t="n">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="D227" t="n">
-        <v>0.5332580588792172</v>
+        <v>0.472500580960615</v>
       </c>
     </row>
     <row r="228">
@@ -3607,13 +3607,13 @@
         <v>0.0008176614881439084</v>
       </c>
       <c r="B228" t="n">
-        <v>0</v>
+        <v>4.440892098500626e-16</v>
       </c>
       <c r="C228" t="n">
-        <v>0.125</v>
+        <v>0.07291666666666667</v>
       </c>
       <c r="D228" t="n">
-        <v>0.5774199869741546</v>
+        <v>0.520400289662169</v>
       </c>
     </row>
     <row r="229">
@@ -3621,13 +3621,13 @@
         <v>0.0008176614881439084</v>
       </c>
       <c r="B229" t="n">
-        <v>0</v>
+        <v>4.440892098500626e-16</v>
       </c>
       <c r="C229" t="n">
-        <v>0.15</v>
+        <v>0.09583333333333333</v>
       </c>
       <c r="D229" t="n">
-        <v>0.6145975884299644</v>
+        <v>0.552211203387685</v>
       </c>
     </row>
     <row r="230">
@@ -3635,13 +3635,13 @@
         <v>0.0008176614881439084</v>
       </c>
       <c r="B230" t="n">
-        <v>0</v>
+        <v>4.440892098500626e-16</v>
       </c>
       <c r="C230" t="n">
-        <v>0.175</v>
+        <v>0.11875</v>
       </c>
       <c r="D230" t="n">
-        <v>0.6455403892564028</v>
+        <v>0.5746577064919347</v>
       </c>
     </row>
     <row r="231">
@@ -3649,13 +3649,13 @@
         <v>0.0008176614881439084</v>
       </c>
       <c r="B231" t="n">
-        <v>0</v>
+        <v>4.440892098500626e-16</v>
       </c>
       <c r="C231" t="n">
-        <v>0.2</v>
+        <v>0.1416666666666667</v>
       </c>
       <c r="D231" t="n">
-        <v>0.6709979154632268</v>
+        <v>0.5944641833296891</v>
       </c>
     </row>
     <row r="232">
@@ -3663,13 +3663,13 @@
         <v>0.0008176614881439084</v>
       </c>
       <c r="B232" t="n">
-        <v>0</v>
+        <v>4.440892098500626e-16</v>
       </c>
       <c r="C232" t="n">
-        <v>0.225</v>
+        <v>0.1645833333333333</v>
       </c>
       <c r="D232" t="n">
-        <v>0.691719693060193</v>
+        <v>0.6175527453576013</v>
       </c>
     </row>
     <row r="233">
@@ -3677,13 +3677,13 @@
         <v>0.0008176614881439084</v>
       </c>
       <c r="B233" t="n">
-        <v>0</v>
+        <v>4.440892098500626e-16</v>
       </c>
       <c r="C233" t="n">
-        <v>0.25</v>
+        <v>0.1875</v>
       </c>
       <c r="D233" t="n">
-        <v>0.708455248057058</v>
+        <v>0.6394136173687387</v>
       </c>
     </row>
     <row r="234">
@@ -3691,13 +3691,13 @@
         <v>0.0008176614881439084</v>
       </c>
       <c r="B234" t="n">
-        <v>0</v>
+        <v>4.440892098500626e-16</v>
       </c>
       <c r="C234" t="n">
-        <v>0.275</v>
+        <v>0.2104166666666666</v>
       </c>
       <c r="D234" t="n">
-        <v>0.7219541064635784</v>
+        <v>0.6487490318896809</v>
       </c>
     </row>
     <row r="235">
@@ -3705,13 +3705,13 @@
         <v>0.0008176614881439084</v>
       </c>
       <c r="B235" t="n">
-        <v>0</v>
+        <v>4.440892098500626e-16</v>
       </c>
       <c r="C235" t="n">
-        <v>0.3</v>
+        <v>0.2333333333333333</v>
       </c>
       <c r="D235" t="n">
-        <v>0.7329657942895109</v>
+        <v>0.6487058615427672</v>
       </c>
     </row>
     <row r="236">
@@ -3719,13 +3719,13 @@
         <v>0.0008176614881439084</v>
       </c>
       <c r="B236" t="n">
-        <v>0</v>
+        <v>4.440892098500626e-16</v>
       </c>
       <c r="C236" t="n">
-        <v>0.325</v>
+        <v>0.25625</v>
       </c>
       <c r="D236" t="n">
-        <v>0.7420786659727926</v>
+        <v>0.6587054799108826</v>
       </c>
     </row>
     <row r="237">
@@ -3733,13 +3733,13 @@
         <v>0.0008176614881439084</v>
       </c>
       <c r="B237" t="n">
-        <v>0</v>
+        <v>4.440892098500626e-16</v>
       </c>
       <c r="C237" t="n">
-        <v>0.35</v>
+        <v>0.2791666666666667</v>
       </c>
       <c r="D237" t="n">
-        <v>0.7492363896640822</v>
+        <v>0.6835880972310554</v>
       </c>
     </row>
     <row r="238">
@@ -3747,13 +3747,13 @@
         <v>0.0008176614881439084</v>
       </c>
       <c r="B238" t="n">
-        <v>0</v>
+        <v>4.440892098500626e-16</v>
       </c>
       <c r="C238" t="n">
-        <v>0.375</v>
+        <v>0.3020833333333333</v>
       </c>
       <c r="D238" t="n">
-        <v>0.7542214619422191</v>
+        <v>0.6999883572614607</v>
       </c>
     </row>
     <row r="239">
@@ -3761,13 +3761,13 @@
         <v>0.0008176614881439084</v>
       </c>
       <c r="B239" t="n">
-        <v>0</v>
+        <v>4.440892098500626e-16</v>
       </c>
       <c r="C239" t="n">
-        <v>0.4</v>
+        <v>0.325</v>
       </c>
       <c r="D239" t="n">
-        <v>0.756816379386042</v>
+        <v>0.6930430732762236</v>
       </c>
     </row>
     <row r="240">
@@ -3775,13 +3775,13 @@
         <v>0.0008176614881439084</v>
       </c>
       <c r="B240" t="n">
-        <v>0</v>
+        <v>4.440892098500626e-16</v>
       </c>
       <c r="C240" t="n">
-        <v>0.4249999999999999</v>
+        <v>0.3479166666666667</v>
       </c>
       <c r="D240" t="n">
-        <v>0.7570305168364901</v>
+        <v>0.6829967568047156</v>
       </c>
     </row>
     <row r="241">
@@ -3789,13 +3789,13 @@
         <v>0.0008176614881439084</v>
       </c>
       <c r="B241" t="n">
-        <v>0</v>
+        <v>4.440892098500626e-16</v>
       </c>
       <c r="C241" t="n">
-        <v>0.45</v>
+        <v>0.3708333333333333</v>
       </c>
       <c r="D241" t="n">
-        <v>0.7557807621829014</v>
+        <v>0.6915158562506398</v>
       </c>
     </row>
     <row r="242">
@@ -3803,13 +3803,13 @@
         <v>0.0008176614881439084</v>
       </c>
       <c r="B242" t="n">
-        <v>0</v>
+        <v>4.440892098500626e-16</v>
       </c>
       <c r="C242" t="n">
-        <v>0.475</v>
+        <v>0.39375</v>
       </c>
       <c r="D242" t="n">
-        <v>0.7542108815767139</v>
+        <v>0.712639931658312</v>
       </c>
     </row>
     <row r="243">
@@ -3817,13 +3817,13 @@
         <v>0.0008176614881439084</v>
       </c>
       <c r="B243" t="n">
-        <v>0</v>
+        <v>4.440892098500626e-16</v>
       </c>
       <c r="C243" t="n">
-        <v>0.5</v>
+        <v>0.4166666666666666</v>
       </c>
       <c r="D243" t="n">
-        <v>0.7534646411693656</v>
+        <v>0.7324332314908819</v>
       </c>
     </row>
     <row r="244">
@@ -3831,13 +3831,13 @@
         <v>0.0008176614881439084</v>
       </c>
       <c r="B244" t="n">
-        <v>0</v>
+        <v>4.440892098500626e-16</v>
       </c>
       <c r="C244" t="n">
-        <v>0.525</v>
+        <v>0.4395833333333333</v>
       </c>
       <c r="D244" t="n">
-        <v>0.7544184344276278</v>
+        <v>0.7470828830391366</v>
       </c>
     </row>
     <row r="245">
@@ -3845,13 +3845,13 @@
         <v>0.0008176614881439084</v>
       </c>
       <c r="B245" t="n">
-        <v>0</v>
+        <v>4.440892098500626e-16</v>
       </c>
       <c r="C245" t="n">
-        <v>0.5499999999999999</v>
+        <v>0.4625</v>
       </c>
       <c r="D245" t="n">
-        <v>0.756879164079606</v>
+        <v>0.7580374387282653</v>
       </c>
     </row>
     <row r="246">
@@ -3859,13 +3859,13 @@
         <v>0.0008176614881439084</v>
       </c>
       <c r="B246" t="n">
-        <v>0</v>
+        <v>4.440892098500626e-16</v>
       </c>
       <c r="C246" t="n">
-        <v>0.575</v>
+        <v>0.4854166666666666</v>
       </c>
       <c r="D246" t="n">
-        <v>0.7603863601687392</v>
+        <v>0.761405703128369</v>
       </c>
     </row>
     <row r="247">
@@ -3873,13 +3873,13 @@
         <v>0.0008176614881439084</v>
       </c>
       <c r="B247" t="n">
-        <v>0</v>
+        <v>4.440892098500626e-16</v>
       </c>
       <c r="C247" t="n">
-        <v>0.6</v>
+        <v>0.5083333333333333</v>
       </c>
       <c r="D247" t="n">
-        <v>0.7644795527384661</v>
+        <v>0.7487208644767908</v>
       </c>
     </row>
     <row r="248">
@@ -3887,13 +3887,13 @@
         <v>0.0008176614881439084</v>
       </c>
       <c r="B248" t="n">
-        <v>0</v>
+        <v>4.440892098500626e-16</v>
       </c>
       <c r="C248" t="n">
-        <v>0.6249999999999999</v>
+        <v>0.53125</v>
       </c>
       <c r="D248" t="n">
-        <v>0.7686982718322257</v>
+        <v>0.7219348349467841</v>
       </c>
     </row>
     <row r="249">
@@ -3901,13 +3901,13 @@
         <v>0.0008176614881439084</v>
       </c>
       <c r="B249" t="n">
-        <v>0</v>
+        <v>4.440892098500626e-16</v>
       </c>
       <c r="C249" t="n">
-        <v>0.6499999999999999</v>
+        <v>0.5541666666666667</v>
       </c>
       <c r="D249" t="n">
-        <v>0.7725820474934572</v>
+        <v>0.6981359665719618</v>
       </c>
     </row>
     <row r="250">
@@ -3915,13 +3915,13 @@
         <v>0.0008176614881439084</v>
       </c>
       <c r="B250" t="n">
-        <v>0</v>
+        <v>4.440892098500626e-16</v>
       </c>
       <c r="C250" t="n">
-        <v>0.6749999999999999</v>
+        <v>0.5770833333333334</v>
       </c>
       <c r="D250" t="n">
-        <v>0.7756704097655991</v>
+        <v>0.6955766918505328</v>
       </c>
     </row>
     <row r="251">
@@ -3929,13 +3929,13 @@
         <v>0.0008176614881439084</v>
       </c>
       <c r="B251" t="n">
-        <v>0</v>
+        <v>4.440892098500626e-16</v>
       </c>
       <c r="C251" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="D251" t="n">
-        <v>0.7775028886920906</v>
+        <v>0.7325094432807069</v>
       </c>
     </row>
     <row r="252">
@@ -3946,10 +3946,10 @@
         <v>2.302585092994046</v>
       </c>
       <c r="C252" t="n">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="D252" t="n">
-        <v>0.6358598282129422</v>
+        <v>0.5343184612864853</v>
       </c>
     </row>
     <row r="253">
@@ -3960,10 +3960,10 @@
         <v>2.302585092994046</v>
       </c>
       <c r="C253" t="n">
-        <v>0.125</v>
+        <v>0.07291666666666667</v>
       </c>
       <c r="D253" t="n">
-        <v>0.6945435138282005</v>
+        <v>0.5995173867648502</v>
       </c>
     </row>
     <row r="254">
@@ -3974,10 +3974,10 @@
         <v>2.302585092994046</v>
       </c>
       <c r="C254" t="n">
-        <v>0.15</v>
+        <v>0.09583333333333333</v>
       </c>
       <c r="D254" t="n">
-        <v>0.7435708241939861</v>
+        <v>0.6502347549238207</v>
       </c>
     </row>
     <row r="255">
@@ -3988,10 +3988,10 @@
         <v>2.302585092994046</v>
       </c>
       <c r="C255" t="n">
-        <v>0.175</v>
+        <v>0.11875</v>
       </c>
       <c r="D255" t="n">
-        <v>0.7840097159885124</v>
+        <v>0.6899650262989592</v>
       </c>
     </row>
     <row r="256">
@@ -4002,10 +4002,10 @@
         <v>2.302585092994046</v>
       </c>
       <c r="C256" t="n">
-        <v>0.2</v>
+        <v>0.1416666666666667</v>
       </c>
       <c r="D256" t="n">
-        <v>0.8169281458899922</v>
+        <v>0.7222026614258281</v>
       </c>
     </row>
     <row r="257">
@@ -4016,10 +4016,10 @@
         <v>2.302585092994046</v>
       </c>
       <c r="C257" t="n">
-        <v>0.225</v>
+        <v>0.1645833333333333</v>
       </c>
       <c r="D257" t="n">
-        <v>0.8433940705766386</v>
+        <v>0.7501866676866104</v>
       </c>
     </row>
     <row r="258">
@@ -4030,10 +4030,10 @@
         <v>2.302585092994046</v>
       </c>
       <c r="C258" t="n">
-        <v>0.25</v>
+        <v>0.1875</v>
       </c>
       <c r="D258" t="n">
-        <v>0.8644754467266649</v>
+        <v>0.7738344167081717</v>
       </c>
     </row>
     <row r="259">
@@ -4044,10 +4044,10 @@
         <v>2.302585092994046</v>
       </c>
       <c r="C259" t="n">
-        <v>0.275</v>
+        <v>0.2104166666666666</v>
       </c>
       <c r="D259" t="n">
-        <v>0.8812402310182839</v>
+        <v>0.7908894778202452</v>
       </c>
     </row>
     <row r="260">
@@ -4058,10 +4058,10 @@
         <v>2.302585092994046</v>
       </c>
       <c r="C260" t="n">
-        <v>0.3</v>
+        <v>0.2333333333333333</v>
       </c>
       <c r="D260" t="n">
-        <v>0.8947563801297088</v>
+        <v>0.8033373074404424</v>
       </c>
     </row>
     <row r="261">
@@ -4072,10 +4072,10 @@
         <v>2.302585092994046</v>
       </c>
       <c r="C261" t="n">
-        <v>0.325</v>
+        <v>0.25625</v>
       </c>
       <c r="D261" t="n">
-        <v>0.9059692183021157</v>
+        <v>0.8179310357681521</v>
       </c>
     </row>
     <row r="262">
@@ -4086,10 +4086,10 @@
         <v>2.302585092994046</v>
       </c>
       <c r="C262" t="n">
-        <v>0.35</v>
+        <v>0.2791666666666667</v>
       </c>
       <c r="D262" t="n">
-        <v>0.9153335400285326</v>
+        <v>0.8356042961599597</v>
       </c>
     </row>
     <row r="263">
@@ -4100,10 +4100,10 @@
         <v>2.302585092994046</v>
       </c>
       <c r="C263" t="n">
-        <v>0.375</v>
+        <v>0.3020833333333333</v>
       </c>
       <c r="D263" t="n">
-        <v>0.9231815073649506</v>
+        <v>0.8462018054542871</v>
       </c>
     </row>
     <row r="264">
@@ -4114,10 +4114,10 @@
         <v>2.302585092994046</v>
       </c>
       <c r="C264" t="n">
-        <v>0.4</v>
+        <v>0.325</v>
       </c>
       <c r="D264" t="n">
-        <v>0.9298452823673606</v>
+        <v>0.8428448693944549</v>
       </c>
     </row>
     <row r="265">
@@ -4128,10 +4128,10 @@
         <v>2.302585092994046</v>
       </c>
       <c r="C265" t="n">
-        <v>0.4249999999999999</v>
+        <v>0.3479166666666667</v>
       </c>
       <c r="D265" t="n">
-        <v>0.9355739399032543</v>
+        <v>0.8322558134136335</v>
       </c>
     </row>
     <row r="266">
@@ -4142,10 +4142,10 @@
         <v>2.302585092994046</v>
       </c>
       <c r="C266" t="n">
-        <v>0.45</v>
+        <v>0.3708333333333333</v>
       </c>
       <c r="D266" t="n">
-        <v>0.9402842060861257</v>
+        <v>0.8236390951260697</v>
       </c>
     </row>
     <row r="267">
@@ -4156,10 +4156,10 @@
         <v>2.302585092994046</v>
       </c>
       <c r="C267" t="n">
-        <v>0.475</v>
+        <v>0.39375</v>
       </c>
       <c r="D267" t="n">
-        <v>0.9438097198409695</v>
+        <v>0.8256566498608001</v>
       </c>
     </row>
     <row r="268">
@@ -4170,10 +4170,10 @@
         <v>2.302585092994046</v>
       </c>
       <c r="C268" t="n">
-        <v>0.5</v>
+        <v>0.4166666666666666</v>
       </c>
       <c r="D268" t="n">
-        <v>0.9459841200927803</v>
+        <v>0.8451131278040587</v>
       </c>
     </row>
     <row r="269">
@@ -4184,10 +4184,10 @@
         <v>2.302585092994046</v>
       </c>
       <c r="C269" t="n">
-        <v>0.525</v>
+        <v>0.4395833333333333</v>
       </c>
       <c r="D269" t="n">
-        <v>0.9467250677114948</v>
+        <v>0.8730316461907067</v>
       </c>
     </row>
     <row r="270">
@@ -4198,10 +4198,10 @@
         <v>2.302585092994046</v>
       </c>
       <c r="C270" t="n">
-        <v>0.5499999999999999</v>
+        <v>0.4625</v>
       </c>
       <c r="D270" t="n">
-        <v>0.946286311346816</v>
+        <v>0.8922882766816016</v>
       </c>
     </row>
     <row r="271">
@@ -4212,10 +4212,10 @@
         <v>2.302585092994046</v>
       </c>
       <c r="C271" t="n">
-        <v>0.575</v>
+        <v>0.4854166666666666</v>
       </c>
       <c r="D271" t="n">
-        <v>0.9450056215933892</v>
+        <v>0.8950389723312445</v>
       </c>
     </row>
     <row r="272">
@@ -4226,10 +4226,10 @@
         <v>2.302585092994046</v>
       </c>
       <c r="C272" t="n">
-        <v>0.6</v>
+        <v>0.5083333333333333</v>
       </c>
       <c r="D272" t="n">
-        <v>0.9432207690458596</v>
+        <v>0.8818709606288094</v>
       </c>
     </row>
     <row r="273">
@@ -4240,10 +4240,10 @@
         <v>2.302585092994046</v>
       </c>
       <c r="C273" t="n">
-        <v>0.6249999999999999</v>
+        <v>0.53125</v>
       </c>
       <c r="D273" t="n">
-        <v>0.9412695242988723</v>
+        <v>0.8590683846090996</v>
       </c>
     </row>
     <row r="274">
@@ -4254,10 +4254,10 @@
         <v>2.302585092994046</v>
       </c>
       <c r="C274" t="n">
-        <v>0.6499999999999999</v>
+        <v>0.5541666666666667</v>
       </c>
       <c r="D274" t="n">
-        <v>0.9394896579470723</v>
+        <v>0.8406480956595033</v>
       </c>
     </row>
     <row r="275">
@@ -4268,10 +4268,10 @@
         <v>2.302585092994046</v>
       </c>
       <c r="C275" t="n">
-        <v>0.6749999999999999</v>
+        <v>0.5770833333333334</v>
       </c>
       <c r="D275" t="n">
-        <v>0.9382189405851048</v>
+        <v>0.8412216355182915</v>
       </c>
     </row>
     <row r="276">
@@ -4282,10 +4282,10 @@
         <v>2.302585092994046</v>
       </c>
       <c r="C276" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="D276" t="n">
-        <v>0.937795142807615</v>
+        <v>0.8754005459237358</v>
       </c>
     </row>
     <row r="277">
@@ -4296,10 +4296,10 @@
         <v>2.70805020110221</v>
       </c>
       <c r="C277" t="n">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="D277" t="n">
-        <v>0.6682277125556288</v>
+        <v>0.5596109469584895</v>
       </c>
     </row>
     <row r="278">
@@ -4310,10 +4310,10 @@
         <v>2.70805020110221</v>
       </c>
       <c r="C278" t="n">
-        <v>0.125</v>
+        <v>0.07291666666666667</v>
       </c>
       <c r="D278" t="n">
-        <v>0.7343681565353751</v>
+        <v>0.627111655501983</v>
       </c>
     </row>
     <row r="279">
@@ -4324,10 +4324,10 @@
         <v>2.70805020110221</v>
       </c>
       <c r="C279" t="n">
-        <v>0.15</v>
+        <v>0.09583333333333333</v>
       </c>
       <c r="D279" t="n">
-        <v>0.7887945082845573</v>
+        <v>0.6768787818085548</v>
       </c>
     </row>
     <row r="280">
@@ -4338,10 +4338,10 @@
         <v>2.70805020110221</v>
       </c>
       <c r="C280" t="n">
-        <v>0.175</v>
+        <v>0.11875</v>
       </c>
       <c r="D280" t="n">
-        <v>0.8328492302792668</v>
+        <v>0.7137363321291528</v>
       </c>
     </row>
     <row r="281">
@@ -4352,10 +4352,10 @@
         <v>2.70805020110221</v>
       </c>
       <c r="C281" t="n">
-        <v>0.2</v>
+        <v>0.1416666666666667</v>
       </c>
       <c r="D281" t="n">
-        <v>0.8678747849955948</v>
+        <v>0.7425083127147249</v>
       </c>
     </row>
     <row r="282">
@@ -4366,10 +4366,10 @@
         <v>2.70805020110221</v>
       </c>
       <c r="C282" t="n">
-        <v>0.225</v>
+        <v>0.1645833333333333</v>
       </c>
       <c r="D282" t="n">
-        <v>0.8952136349096325</v>
+        <v>0.7677243819192431</v>
       </c>
     </row>
     <row r="283">
@@ -4380,10 +4380,10 @@
         <v>2.70805020110221</v>
       </c>
       <c r="C283" t="n">
-        <v>0.25</v>
+        <v>0.1875</v>
       </c>
       <c r="D283" t="n">
-        <v>0.9162082424974712</v>
+        <v>0.7900868172788509</v>
       </c>
     </row>
     <row r="284">
@@ -4394,10 +4394,10 @@
         <v>2.70805020110221</v>
       </c>
       <c r="C284" t="n">
-        <v>0.275</v>
+        <v>0.2104166666666666</v>
       </c>
       <c r="D284" t="n">
-        <v>0.9322010702352025</v>
+        <v>0.8077115536328834</v>
       </c>
     </row>
     <row r="285">
@@ -4408,10 +4408,10 @@
         <v>2.70805020110221</v>
       </c>
       <c r="C285" t="n">
-        <v>0.3</v>
+        <v>0.2333333333333333</v>
       </c>
       <c r="D285" t="n">
-        <v>0.9445345805989173</v>
+        <v>0.8212558986260661</v>
       </c>
     </row>
     <row r="286">
@@ -4422,10 +4422,10 @@
         <v>2.70805020110221</v>
       </c>
       <c r="C286" t="n">
-        <v>0.325</v>
+        <v>0.25625</v>
       </c>
       <c r="D286" t="n">
-        <v>0.9544157757625321</v>
+        <v>0.8342772975068115</v>
       </c>
     </row>
     <row r="287">
@@ -4436,10 +4436,10 @@
         <v>2.70805020110221</v>
       </c>
       <c r="C287" t="n">
-        <v>0.35</v>
+        <v>0.2791666666666667</v>
       </c>
       <c r="D287" t="n">
-        <v>0.9625098166912641</v>
+        <v>0.8482220791650839</v>
       </c>
     </row>
     <row r="288">
@@ -4450,10 +4450,10 @@
         <v>2.70805020110221</v>
       </c>
       <c r="C288" t="n">
-        <v>0.375</v>
+        <v>0.3020833333333333</v>
       </c>
       <c r="D288" t="n">
-        <v>0.9693464040481559</v>
+        <v>0.8603991233517826</v>
       </c>
     </row>
     <row r="289">
@@ -4464,10 +4464,10 @@
         <v>2.70805020110221</v>
       </c>
       <c r="C289" t="n">
-        <v>0.4</v>
+        <v>0.325</v>
       </c>
       <c r="D289" t="n">
-        <v>0.9754552384962497</v>
+        <v>0.8680334035859287</v>
       </c>
     </row>
     <row r="290">
@@ -4478,10 +4478,10 @@
         <v>2.70805020110221</v>
       </c>
       <c r="C290" t="n">
-        <v>0.4249999999999999</v>
+        <v>0.3479166666666667</v>
       </c>
       <c r="D290" t="n">
-        <v>0.9812450944075913</v>
+        <v>0.8694375978585214</v>
       </c>
     </row>
     <row r="291">
@@ -4492,10 +4492,10 @@
         <v>2.70805020110221</v>
       </c>
       <c r="C291" t="n">
-        <v>0.45</v>
+        <v>0.3708333333333333</v>
       </c>
       <c r="D291" t="n">
-        <v>0.9866410409902404</v>
+        <v>0.8646618969554255</v>
       </c>
     </row>
     <row r="292">
@@ -4506,10 +4506,10 @@
         <v>2.70805020110221</v>
       </c>
       <c r="C292" t="n">
-        <v>0.475</v>
+        <v>0.39375</v>
       </c>
       <c r="D292" t="n">
-        <v>0.9914472211612601</v>
+        <v>0.8618098420043123</v>
       </c>
     </row>
     <row r="293">
@@ -4520,10 +4520,10 @@
         <v>2.70805020110221</v>
       </c>
       <c r="C293" t="n">
-        <v>0.5</v>
+        <v>0.4166666666666666</v>
       </c>
       <c r="D293" t="n">
-        <v>0.9954677778377136</v>
+        <v>0.8703711108902301</v>
       </c>
     </row>
     <row r="294">
@@ -4534,10 +4534,10 @@
         <v>2.70805020110221</v>
       </c>
       <c r="C294" t="n">
-        <v>0.525</v>
+        <v>0.4395833333333333</v>
       </c>
       <c r="D294" t="n">
-        <v>0.998510344125115</v>
+        <v>0.8880640505435662</v>
       </c>
     </row>
     <row r="295">
@@ -4548,10 +4548,10 @@
         <v>2.70805020110221</v>
       </c>
       <c r="C295" t="n">
-        <v>0.5499999999999999</v>
+        <v>0.4625</v>
       </c>
       <c r="D295" t="n">
-        <v>1</v>
+        <v>0.906252667137716</v>
       </c>
     </row>
     <row r="296">
@@ -4562,10 +4562,10 @@
         <v>2.70805020110221</v>
       </c>
       <c r="C296" t="n">
-        <v>0.575</v>
+        <v>0.4854166666666666</v>
       </c>
       <c r="D296" t="n">
-        <v>1</v>
+        <v>0.9180370780357946</v>
       </c>
     </row>
     <row r="297">
@@ -4576,10 +4576,10 @@
         <v>2.70805020110221</v>
       </c>
       <c r="C297" t="n">
-        <v>0.6</v>
+        <v>0.5083333333333333</v>
       </c>
       <c r="D297" t="n">
-        <v>1</v>
+        <v>0.9182340899111683</v>
       </c>
     </row>
     <row r="298">
@@ -4590,10 +4590,10 @@
         <v>2.70805020110221</v>
       </c>
       <c r="C298" t="n">
-        <v>0.6249999999999999</v>
+        <v>0.53125</v>
       </c>
       <c r="D298" t="n">
-        <v>0.9973674844550885</v>
+        <v>0.9073758824267638</v>
       </c>
     </row>
     <row r="299">
@@ -4604,10 +4604,10 @@
         <v>2.70805020110221</v>
       </c>
       <c r="C299" t="n">
-        <v>0.6499999999999999</v>
+        <v>0.5541666666666667</v>
       </c>
       <c r="D299" t="n">
-        <v>0.9928789085715235</v>
+        <v>0.8940877497398398</v>
       </c>
     </row>
     <row r="300">
@@ -4618,10 +4618,10 @@
         <v>2.70805020110221</v>
       </c>
       <c r="C300" t="n">
-        <v>0.6749999999999999</v>
+        <v>0.5770833333333334</v>
       </c>
       <c r="D300" t="n">
-        <v>0.9863593563970755</v>
+        <v>0.8876173936918611</v>
       </c>
     </row>
     <row r="301">
@@ -4632,10 +4632,1410 @@
         <v>2.70805020110221</v>
       </c>
       <c r="C301" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="D301" t="n">
-        <v>0.9776339119795139</v>
+        <v>0.8972125161242921</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="n">
+        <v>0.0008525149190110827</v>
+      </c>
+      <c r="B302" t="n">
+        <v>-2.302585092994045</v>
+      </c>
+      <c r="C302" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D302" t="n">
+        <v>0.4538896227313606</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="n">
+        <v>0.0008525149190110827</v>
+      </c>
+      <c r="B303" t="n">
+        <v>-2.302585092994045</v>
+      </c>
+      <c r="C303" t="n">
+        <v>0.07291666666666667</v>
+      </c>
+      <c r="D303" t="n">
+        <v>0.4823012097995297</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="n">
+        <v>0.0008525149190110827</v>
+      </c>
+      <c r="B304" t="n">
+        <v>-2.302585092994045</v>
+      </c>
+      <c r="C304" t="n">
+        <v>0.09583333333333333</v>
+      </c>
+      <c r="D304" t="n">
+        <v>0.5235054591089211</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="n">
+        <v>0.0008525149190110827</v>
+      </c>
+      <c r="B305" t="n">
+        <v>-2.302585092994045</v>
+      </c>
+      <c r="C305" t="n">
+        <v>0.11875</v>
+      </c>
+      <c r="D305" t="n">
+        <v>0.5666449659119952</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="n">
+        <v>0.0008525149190110827</v>
+      </c>
+      <c r="B306" t="n">
+        <v>-2.302585092994045</v>
+      </c>
+      <c r="C306" t="n">
+        <v>0.1416666666666667</v>
+      </c>
+      <c r="D306" t="n">
+        <v>0.6008623254612122</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="n">
+        <v>0.0008525149190110827</v>
+      </c>
+      <c r="B307" t="n">
+        <v>-2.302585092994045</v>
+      </c>
+      <c r="C307" t="n">
+        <v>0.1645833333333333</v>
+      </c>
+      <c r="D307" t="n">
+        <v>0.6164971036694684</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="n">
+        <v>0.0008525149190110827</v>
+      </c>
+      <c r="B308" t="n">
+        <v>-2.302585092994045</v>
+      </c>
+      <c r="C308" t="n">
+        <v>0.1875</v>
+      </c>
+      <c r="D308" t="n">
+        <v>0.6194529747457115</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="n">
+        <v>0.0008525149190110827</v>
+      </c>
+      <c r="B309" t="n">
+        <v>-2.302585092994045</v>
+      </c>
+      <c r="C309" t="n">
+        <v>0.2104166666666666</v>
+      </c>
+      <c r="D309" t="n">
+        <v>0.6261696061819513</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="n">
+        <v>0.0008525149190110827</v>
+      </c>
+      <c r="B310" t="n">
+        <v>-2.302585092994045</v>
+      </c>
+      <c r="C310" t="n">
+        <v>0.2333333333333333</v>
+      </c>
+      <c r="D310" t="n">
+        <v>0.6432868504437964</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="n">
+        <v>0.0008525149190110827</v>
+      </c>
+      <c r="B311" t="n">
+        <v>-2.302585092994045</v>
+      </c>
+      <c r="C311" t="n">
+        <v>0.25625</v>
+      </c>
+      <c r="D311" t="n">
+        <v>0.6661273831112443</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="n">
+        <v>0.0008525149190110827</v>
+      </c>
+      <c r="B312" t="n">
+        <v>-2.302585092994045</v>
+      </c>
+      <c r="C312" t="n">
+        <v>0.2791666666666667</v>
+      </c>
+      <c r="D312" t="n">
+        <v>0.6863491547000303</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="n">
+        <v>0.0008525149190110827</v>
+      </c>
+      <c r="B313" t="n">
+        <v>-2.302585092994045</v>
+      </c>
+      <c r="C313" t="n">
+        <v>0.3020833333333333</v>
+      </c>
+      <c r="D313" t="n">
+        <v>0.6900254141863342</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="n">
+        <v>0.0008525149190110827</v>
+      </c>
+      <c r="B314" t="n">
+        <v>-2.302585092994045</v>
+      </c>
+      <c r="C314" t="n">
+        <v>0.325</v>
+      </c>
+      <c r="D314" t="n">
+        <v>0.6712783026371758</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="n">
+        <v>0.0008525149190110827</v>
+      </c>
+      <c r="B315" t="n">
+        <v>-2.302585092994045</v>
+      </c>
+      <c r="C315" t="n">
+        <v>0.3479166666666667</v>
+      </c>
+      <c r="D315" t="n">
+        <v>0.6506074833984384</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="n">
+        <v>0.0008525149190110827</v>
+      </c>
+      <c r="B316" t="n">
+        <v>-2.302585092994045</v>
+      </c>
+      <c r="C316" t="n">
+        <v>0.3708333333333333</v>
+      </c>
+      <c r="D316" t="n">
+        <v>0.6494077494580861</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="n">
+        <v>0.0008525149190110827</v>
+      </c>
+      <c r="B317" t="n">
+        <v>-2.302585092994045</v>
+      </c>
+      <c r="C317" t="n">
+        <v>0.39375</v>
+      </c>
+      <c r="D317" t="n">
+        <v>0.6674056485722022</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="n">
+        <v>0.0008525149190110827</v>
+      </c>
+      <c r="B318" t="n">
+        <v>-2.302585092994045</v>
+      </c>
+      <c r="C318" t="n">
+        <v>0.4166666666666666</v>
+      </c>
+      <c r="D318" t="n">
+        <v>0.6968330859806028</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="n">
+        <v>0.0008525149190110827</v>
+      </c>
+      <c r="B319" t="n">
+        <v>-2.302585092994045</v>
+      </c>
+      <c r="C319" t="n">
+        <v>0.4395833333333333</v>
+      </c>
+      <c r="D319" t="n">
+        <v>0.7262148734567466</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="n">
+        <v>0.0008525149190110827</v>
+      </c>
+      <c r="B320" t="n">
+        <v>-2.302585092994045</v>
+      </c>
+      <c r="C320" t="n">
+        <v>0.4625</v>
+      </c>
+      <c r="D320" t="n">
+        <v>0.7423491158391793</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="n">
+        <v>0.0008525149190110827</v>
+      </c>
+      <c r="B321" t="n">
+        <v>-2.302585092994045</v>
+      </c>
+      <c r="C321" t="n">
+        <v>0.4854166666666666</v>
+      </c>
+      <c r="D321" t="n">
+        <v>0.7376778717107506</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="n">
+        <v>0.0008525149190110827</v>
+      </c>
+      <c r="B322" t="n">
+        <v>-2.302585092994045</v>
+      </c>
+      <c r="C322" t="n">
+        <v>0.5083333333333333</v>
+      </c>
+      <c r="D322" t="n">
+        <v>0.7098986504858548</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="n">
+        <v>0.0008525149190110827</v>
+      </c>
+      <c r="B323" t="n">
+        <v>-2.302585092994045</v>
+      </c>
+      <c r="C323" t="n">
+        <v>0.53125</v>
+      </c>
+      <c r="D323" t="n">
+        <v>0.6678238860307593</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="n">
+        <v>0.0008525149190110827</v>
+      </c>
+      <c r="B324" t="n">
+        <v>-2.302585092994045</v>
+      </c>
+      <c r="C324" t="n">
+        <v>0.5541666666666667</v>
+      </c>
+      <c r="D324" t="n">
+        <v>0.6359096785060858</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="n">
+        <v>0.0008525149190110827</v>
+      </c>
+      <c r="B325" t="n">
+        <v>-2.302585092994045</v>
+      </c>
+      <c r="C325" t="n">
+        <v>0.5770833333333334</v>
+      </c>
+      <c r="D325" t="n">
+        <v>0.6398152172067525</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="n">
+        <v>0.0008525149190110827</v>
+      </c>
+      <c r="B326" t="n">
+        <v>-2.302585092994045</v>
+      </c>
+      <c r="C326" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D326" t="n">
+        <v>0.705199691427677</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="n">
+        <v>0.0008525149190110827</v>
+      </c>
+      <c r="B327" t="n">
+        <v>4.440892098500626e-16</v>
+      </c>
+      <c r="C327" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D327" t="n">
+        <v>0.5173326154458291</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="n">
+        <v>0.0008525149190110827</v>
+      </c>
+      <c r="B328" t="n">
+        <v>4.440892098500626e-16</v>
+      </c>
+      <c r="C328" t="n">
+        <v>0.07291666666666667</v>
+      </c>
+      <c r="D328" t="n">
+        <v>0.5769959497505391</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="n">
+        <v>0.0008525149190110827</v>
+      </c>
+      <c r="B329" t="n">
+        <v>4.440892098500626e-16</v>
+      </c>
+      <c r="C329" t="n">
+        <v>0.09583333333333333</v>
+      </c>
+      <c r="D329" t="n">
+        <v>0.6284983743802151</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="n">
+        <v>0.0008525149190110827</v>
+      </c>
+      <c r="B330" t="n">
+        <v>4.440892098500626e-16</v>
+      </c>
+      <c r="C330" t="n">
+        <v>0.11875</v>
+      </c>
+      <c r="D330" t="n">
+        <v>0.670781817527198</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="n">
+        <v>0.0008525149190110827</v>
+      </c>
+      <c r="B331" t="n">
+        <v>4.440892098500626e-16</v>
+      </c>
+      <c r="C331" t="n">
+        <v>0.1416666666666667</v>
+      </c>
+      <c r="D331" t="n">
+        <v>0.7027882073838286</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="n">
+        <v>0.0008525149190110827</v>
+      </c>
+      <c r="B332" t="n">
+        <v>4.440892098500626e-16</v>
+      </c>
+      <c r="C332" t="n">
+        <v>0.1645833333333333</v>
+      </c>
+      <c r="D332" t="n">
+        <v>0.7238232235554483</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="n">
+        <v>0.0008525149190110827</v>
+      </c>
+      <c r="B333" t="n">
+        <v>4.440892098500626e-16</v>
+      </c>
+      <c r="C333" t="n">
+        <v>0.1875</v>
+      </c>
+      <c r="D333" t="n">
+        <v>0.7379223745161457</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="n">
+        <v>0.0008525149190110827</v>
+      </c>
+      <c r="B334" t="n">
+        <v>4.440892098500626e-16</v>
+      </c>
+      <c r="C334" t="n">
+        <v>0.2104166666666666</v>
+      </c>
+      <c r="D334" t="n">
+        <v>0.7523178374421485</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="n">
+        <v>0.0008525149190110827</v>
+      </c>
+      <c r="B335" t="n">
+        <v>4.440892098500626e-16</v>
+      </c>
+      <c r="C335" t="n">
+        <v>0.2333333333333333</v>
+      </c>
+      <c r="D335" t="n">
+        <v>0.7711155502594017</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="n">
+        <v>0.0008525149190110827</v>
+      </c>
+      <c r="B336" t="n">
+        <v>4.440892098500626e-16</v>
+      </c>
+      <c r="C336" t="n">
+        <v>0.25625</v>
+      </c>
+      <c r="D336" t="n">
+        <v>0.794768853355787</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="n">
+        <v>0.0008525149190110827</v>
+      </c>
+      <c r="B337" t="n">
+        <v>4.440892098500626e-16</v>
+      </c>
+      <c r="C337" t="n">
+        <v>0.2791666666666667</v>
+      </c>
+      <c r="D337" t="n">
+        <v>0.8180608812297024</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="n">
+        <v>0.0008525149190110827</v>
+      </c>
+      <c r="B338" t="n">
+        <v>4.440892098500626e-16</v>
+      </c>
+      <c r="C338" t="n">
+        <v>0.3020833333333333</v>
+      </c>
+      <c r="D338" t="n">
+        <v>0.8257809873891079</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="n">
+        <v>0.0008525149190110827</v>
+      </c>
+      <c r="B339" t="n">
+        <v>4.440892098500626e-16</v>
+      </c>
+      <c r="C339" t="n">
+        <v>0.325</v>
+      </c>
+      <c r="D339" t="n">
+        <v>0.8099710436994441</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="n">
+        <v>0.0008525149190110827</v>
+      </c>
+      <c r="B340" t="n">
+        <v>4.440892098500626e-16</v>
+      </c>
+      <c r="C340" t="n">
+        <v>0.3479166666666667</v>
+      </c>
+      <c r="D340" t="n">
+        <v>0.7880520522747437</v>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="n">
+        <v>0.0008525149190110827</v>
+      </c>
+      <c r="B341" t="n">
+        <v>4.440892098500626e-16</v>
+      </c>
+      <c r="C341" t="n">
+        <v>0.3708333333333333</v>
+      </c>
+      <c r="D341" t="n">
+        <v>0.7795392977743035</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="n">
+        <v>0.0008525149190110827</v>
+      </c>
+      <c r="B342" t="n">
+        <v>4.440892098500626e-16</v>
+      </c>
+      <c r="C342" t="n">
+        <v>0.39375</v>
+      </c>
+      <c r="D342" t="n">
+        <v>0.7895869550794571</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="n">
+        <v>0.0008525149190110827</v>
+      </c>
+      <c r="B343" t="n">
+        <v>4.440892098500626e-16</v>
+      </c>
+      <c r="C343" t="n">
+        <v>0.4166666666666666</v>
+      </c>
+      <c r="D343" t="n">
+        <v>0.8174745084517924</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="n">
+        <v>0.0008525149190110827</v>
+      </c>
+      <c r="B344" t="n">
+        <v>4.440892098500626e-16</v>
+      </c>
+      <c r="C344" t="n">
+        <v>0.4395833333333333</v>
+      </c>
+      <c r="D344" t="n">
+        <v>0.8514976423350379</v>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="n">
+        <v>0.0008525149190110827</v>
+      </c>
+      <c r="B345" t="n">
+        <v>4.440892098500626e-16</v>
+      </c>
+      <c r="C345" t="n">
+        <v>0.4625</v>
+      </c>
+      <c r="D345" t="n">
+        <v>0.8743924321517429</v>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="n">
+        <v>0.0008525149190110827</v>
+      </c>
+      <c r="B346" t="n">
+        <v>4.440892098500626e-16</v>
+      </c>
+      <c r="C346" t="n">
+        <v>0.4854166666666666</v>
+      </c>
+      <c r="D346" t="n">
+        <v>0.8774007191113203</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="n">
+        <v>0.0008525149190110827</v>
+      </c>
+      <c r="B347" t="n">
+        <v>4.440892098500626e-16</v>
+      </c>
+      <c r="C347" t="n">
+        <v>0.5083333333333333</v>
+      </c>
+      <c r="D347" t="n">
+        <v>0.8595394899281619</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="n">
+        <v>0.0008525149190110827</v>
+      </c>
+      <c r="B348" t="n">
+        <v>4.440892098500626e-16</v>
+      </c>
+      <c r="C348" t="n">
+        <v>0.53125</v>
+      </c>
+      <c r="D348" t="n">
+        <v>0.8281931835377001</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="n">
+        <v>0.0008525149190110827</v>
+      </c>
+      <c r="B349" t="n">
+        <v>4.440892098500626e-16</v>
+      </c>
+      <c r="C349" t="n">
+        <v>0.5541666666666667</v>
+      </c>
+      <c r="D349" t="n">
+        <v>0.8023330317456945</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="n">
+        <v>0.0008525149190110827</v>
+      </c>
+      <c r="B350" t="n">
+        <v>4.440892098500626e-16</v>
+      </c>
+      <c r="C350" t="n">
+        <v>0.5770833333333334</v>
+      </c>
+      <c r="D350" t="n">
+        <v>0.8018213582759594</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="n">
+        <v>0.0008525149190110827</v>
+      </c>
+      <c r="B351" t="n">
+        <v>4.440892098500626e-16</v>
+      </c>
+      <c r="C351" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D351" t="n">
+        <v>0.8465204868523086</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="n">
+        <v>0.0008525149190110827</v>
+      </c>
+      <c r="B352" t="n">
+        <v>2.302585092994046</v>
+      </c>
+      <c r="C352" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D352" t="n">
+        <v>0.5940920313311207</v>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="n">
+        <v>0.0008525149190110827</v>
+      </c>
+      <c r="B353" t="n">
+        <v>2.302585092994046</v>
+      </c>
+      <c r="C353" t="n">
+        <v>0.07291666666666667</v>
+      </c>
+      <c r="D353" t="n">
+        <v>0.6702265237364894</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="n">
+        <v>0.0008525149190110827</v>
+      </c>
+      <c r="B354" t="n">
+        <v>2.302585092994046</v>
+      </c>
+      <c r="C354" t="n">
+        <v>0.09583333333333333</v>
+      </c>
+      <c r="D354" t="n">
+        <v>0.7278423024739099</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="n">
+        <v>0.0008525149190110827</v>
+      </c>
+      <c r="B355" t="n">
+        <v>2.302585092994046</v>
+      </c>
+      <c r="C355" t="n">
+        <v>0.11875</v>
+      </c>
+      <c r="D355" t="n">
+        <v>0.7717676623199041</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="n">
+        <v>0.0008525149190110827</v>
+      </c>
+      <c r="B356" t="n">
+        <v>2.302585092994046</v>
+      </c>
+      <c r="C356" t="n">
+        <v>0.1416666666666667</v>
+      </c>
+      <c r="D356" t="n">
+        <v>0.8068308980509939</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="n">
+        <v>0.0008525149190110827</v>
+      </c>
+      <c r="B357" t="n">
+        <v>2.302585092994046</v>
+      </c>
+      <c r="C357" t="n">
+        <v>0.1645833333333333</v>
+      </c>
+      <c r="D357" t="n">
+        <v>0.837523647586256</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="n">
+        <v>0.0008525149190110827</v>
+      </c>
+      <c r="B358" t="n">
+        <v>2.302585092994046</v>
+      </c>
+      <c r="C358" t="n">
+        <v>0.1875</v>
+      </c>
+      <c r="D358" t="n">
+        <v>0.8639600281911074</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="n">
+        <v>0.0008525149190110827</v>
+      </c>
+      <c r="B359" t="n">
+        <v>2.302585092994046</v>
+      </c>
+      <c r="C359" t="n">
+        <v>0.2104166666666666</v>
+      </c>
+      <c r="D359" t="n">
+        <v>0.8833309173745968</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="n">
+        <v>0.0008525149190110827</v>
+      </c>
+      <c r="B360" t="n">
+        <v>2.302585092994046</v>
+      </c>
+      <c r="C360" t="n">
+        <v>0.2333333333333333</v>
+      </c>
+      <c r="D360" t="n">
+        <v>0.8967366668406629</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="n">
+        <v>0.0008525149190110827</v>
+      </c>
+      <c r="B361" t="n">
+        <v>2.302585092994046</v>
+      </c>
+      <c r="C361" t="n">
+        <v>0.25625</v>
+      </c>
+      <c r="D361" t="n">
+        <v>0.909724023500186</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="n">
+        <v>0.0008525149190110827</v>
+      </c>
+      <c r="B362" t="n">
+        <v>2.302585092994046</v>
+      </c>
+      <c r="C362" t="n">
+        <v>0.2791666666666667</v>
+      </c>
+      <c r="D362" t="n">
+        <v>0.9255108725990207</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="n">
+        <v>0.0008525149190110827</v>
+      </c>
+      <c r="B363" t="n">
+        <v>2.302585092994046</v>
+      </c>
+      <c r="C363" t="n">
+        <v>0.3020833333333333</v>
+      </c>
+      <c r="D363" t="n">
+        <v>0.9426277668721793</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="n">
+        <v>0.0008525149190110827</v>
+      </c>
+      <c r="B364" t="n">
+        <v>2.302585092994046</v>
+      </c>
+      <c r="C364" t="n">
+        <v>0.325</v>
+      </c>
+      <c r="D364" t="n">
+        <v>0.956661741295291</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="n">
+        <v>0.0008525149190110827</v>
+      </c>
+      <c r="B365" t="n">
+        <v>2.302585092994046</v>
+      </c>
+      <c r="C365" t="n">
+        <v>0.3479166666666667</v>
+      </c>
+      <c r="D365" t="n">
+        <v>0.9557391294853349</v>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="n">
+        <v>0.0008525149190110827</v>
+      </c>
+      <c r="B366" t="n">
+        <v>2.302585092994046</v>
+      </c>
+      <c r="C366" t="n">
+        <v>0.3708333333333333</v>
+      </c>
+      <c r="D366" t="n">
+        <v>0.9326811056750299</v>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="n">
+        <v>0.0008525149190110827</v>
+      </c>
+      <c r="B367" t="n">
+        <v>2.302585092994046</v>
+      </c>
+      <c r="C367" t="n">
+        <v>0.39375</v>
+      </c>
+      <c r="D367" t="n">
+        <v>0.9124691019351547</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="n">
+        <v>0.0008525149190110827</v>
+      </c>
+      <c r="B368" t="n">
+        <v>2.302585092994046</v>
+      </c>
+      <c r="C368" t="n">
+        <v>0.4166666666666666</v>
+      </c>
+      <c r="D368" t="n">
+        <v>0.9261260650016304</v>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="n">
+        <v>0.0008525149190110827</v>
+      </c>
+      <c r="B369" t="n">
+        <v>2.302585092994046</v>
+      </c>
+      <c r="C369" t="n">
+        <v>0.4395833333333333</v>
+      </c>
+      <c r="D369" t="n">
+        <v>0.9624229945337043</v>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="n">
+        <v>0.0008525149190110827</v>
+      </c>
+      <c r="B370" t="n">
+        <v>2.302585092994046</v>
+      </c>
+      <c r="C370" t="n">
+        <v>0.4625</v>
+      </c>
+      <c r="D370" t="n">
+        <v>0.9881181332857701</v>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="n">
+        <v>0.0008525149190110827</v>
+      </c>
+      <c r="B371" t="n">
+        <v>2.302585092994046</v>
+      </c>
+      <c r="C371" t="n">
+        <v>0.4854166666666666</v>
+      </c>
+      <c r="D371" t="n">
+        <v>0.9911191701695794</v>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="n">
+        <v>0.0008525149190110827</v>
+      </c>
+      <c r="B372" t="n">
+        <v>2.302585092994046</v>
+      </c>
+      <c r="C372" t="n">
+        <v>0.5083333333333333</v>
+      </c>
+      <c r="D372" t="n">
+        <v>0.9783648899188228</v>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="n">
+        <v>0.0008525149190110827</v>
+      </c>
+      <c r="B373" t="n">
+        <v>2.302585092994046</v>
+      </c>
+      <c r="C373" t="n">
+        <v>0.53125</v>
+      </c>
+      <c r="D373" t="n">
+        <v>0.9592679046838072</v>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="n">
+        <v>0.0008525149190110827</v>
+      </c>
+      <c r="B374" t="n">
+        <v>2.302585092994046</v>
+      </c>
+      <c r="C374" t="n">
+        <v>0.5541666666666667</v>
+      </c>
+      <c r="D374" t="n">
+        <v>0.9458341529078568</v>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="n">
+        <v>0.0008525149190110827</v>
+      </c>
+      <c r="B375" t="n">
+        <v>2.302585092994046</v>
+      </c>
+      <c r="C375" t="n">
+        <v>0.5770833333333334</v>
+      </c>
+      <c r="D375" t="n">
+        <v>0.9502690149442744</v>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="n">
+        <v>0.0008525149190110827</v>
+      </c>
+      <c r="B376" t="n">
+        <v>2.302585092994046</v>
+      </c>
+      <c r="C376" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D376" t="n">
+        <v>0.9847778711463628</v>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="n">
+        <v>0.0008525149190110827</v>
+      </c>
+      <c r="B377" t="n">
+        <v>2.70805020110221</v>
+      </c>
+      <c r="C377" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D377" t="n">
+        <v>0.6005755890774299</v>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="n">
+        <v>0.0008525149190110827</v>
+      </c>
+      <c r="B378" t="n">
+        <v>2.70805020110221</v>
+      </c>
+      <c r="C378" t="n">
+        <v>0.07291666666666667</v>
+      </c>
+      <c r="D378" t="n">
+        <v>0.6826307748067543</v>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="n">
+        <v>0.0008525149190110827</v>
+      </c>
+      <c r="B379" t="n">
+        <v>2.70805020110221</v>
+      </c>
+      <c r="C379" t="n">
+        <v>0.09583333333333333</v>
+      </c>
+      <c r="D379" t="n">
+        <v>0.7444334591942281</v>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="n">
+        <v>0.0008525149190110827</v>
+      </c>
+      <c r="B380" t="n">
+        <v>2.70805020110221</v>
+      </c>
+      <c r="C380" t="n">
+        <v>0.11875</v>
+      </c>
+      <c r="D380" t="n">
+        <v>0.7907915343867048</v>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="n">
+        <v>0.0008525149190110827</v>
+      </c>
+      <c r="B381" t="n">
+        <v>2.70805020110221</v>
+      </c>
+      <c r="C381" t="n">
+        <v>0.1416666666666667</v>
+      </c>
+      <c r="D381" t="n">
+        <v>0.8265128925310378</v>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="n">
+        <v>0.0008525149190110827</v>
+      </c>
+      <c r="B382" t="n">
+        <v>2.70805020110221</v>
+      </c>
+      <c r="C382" t="n">
+        <v>0.1645833333333333</v>
+      </c>
+      <c r="D382" t="n">
+        <v>0.8561588543703873</v>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="n">
+        <v>0.0008525149190110827</v>
+      </c>
+      <c r="B383" t="n">
+        <v>2.70805020110221</v>
+      </c>
+      <c r="C383" t="n">
+        <v>0.1875</v>
+      </c>
+      <c r="D383" t="n">
+        <v>0.881084593532842</v>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="n">
+        <v>0.0008525149190110827</v>
+      </c>
+      <c r="B384" t="n">
+        <v>2.70805020110221</v>
+      </c>
+      <c r="C384" t="n">
+        <v>0.2104166666666666</v>
+      </c>
+      <c r="D384" t="n">
+        <v>0.9004805209350033</v>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="n">
+        <v>0.0008525149190110827</v>
+      </c>
+      <c r="B385" t="n">
+        <v>2.70805020110221</v>
+      </c>
+      <c r="C385" t="n">
+        <v>0.2333333333333333</v>
+      </c>
+      <c r="D385" t="n">
+        <v>0.9157172133583712</v>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="n">
+        <v>0.0008525149190110827</v>
+      </c>
+      <c r="B386" t="n">
+        <v>2.70805020110221</v>
+      </c>
+      <c r="C386" t="n">
+        <v>0.25625</v>
+      </c>
+      <c r="D386" t="n">
+        <v>0.9306535099028792</v>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="n">
+        <v>0.0008525149190110827</v>
+      </c>
+      <c r="B387" t="n">
+        <v>2.70805020110221</v>
+      </c>
+      <c r="C387" t="n">
+        <v>0.2791666666666667</v>
+      </c>
+      <c r="D387" t="n">
+        <v>0.9474905185374413</v>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="n">
+        <v>0.0008525149190110827</v>
+      </c>
+      <c r="B388" t="n">
+        <v>2.70805020110221</v>
+      </c>
+      <c r="C388" t="n">
+        <v>0.3020833333333333</v>
+      </c>
+      <c r="D388" t="n">
+        <v>0.9651581559367521</v>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="n">
+        <v>0.0008525149190110827</v>
+      </c>
+      <c r="B389" t="n">
+        <v>2.70805020110221</v>
+      </c>
+      <c r="C389" t="n">
+        <v>0.325</v>
+      </c>
+      <c r="D389" t="n">
+        <v>0.9794955597395784</v>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="n">
+        <v>0.0008525149190110827</v>
+      </c>
+      <c r="B390" t="n">
+        <v>2.70805020110221</v>
+      </c>
+      <c r="C390" t="n">
+        <v>0.3479166666666667</v>
+      </c>
+      <c r="D390" t="n">
+        <v>0.9779718147100437</v>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="n">
+        <v>0.0008525149190110827</v>
+      </c>
+      <c r="B391" t="n">
+        <v>2.70805020110221</v>
+      </c>
+      <c r="C391" t="n">
+        <v>0.3708333333333333</v>
+      </c>
+      <c r="D391" t="n">
+        <v>0.9529848380736604</v>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="n">
+        <v>0.0008525149190110827</v>
+      </c>
+      <c r="B392" t="n">
+        <v>2.70805020110221</v>
+      </c>
+      <c r="C392" t="n">
+        <v>0.39375</v>
+      </c>
+      <c r="D392" t="n">
+        <v>0.9312331875099413</v>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="n">
+        <v>0.0008525149190110827</v>
+      </c>
+      <c r="B393" t="n">
+        <v>2.70805020110221</v>
+      </c>
+      <c r="C393" t="n">
+        <v>0.4166666666666666</v>
+      </c>
+      <c r="D393" t="n">
+        <v>0.9456880914546928</v>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="n">
+        <v>0.0008525149190110827</v>
+      </c>
+      <c r="B394" t="n">
+        <v>2.70805020110221</v>
+      </c>
+      <c r="C394" t="n">
+        <v>0.4395833333333333</v>
+      </c>
+      <c r="D394" t="n">
+        <v>0.9826506803129755</v>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="n">
+        <v>0.0008525149190110827</v>
+      </c>
+      <c r="B395" t="n">
+        <v>2.70805020110221</v>
+      </c>
+      <c r="C395" t="n">
+        <v>0.4625</v>
+      </c>
+      <c r="D395" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="n">
+        <v>0.0008525149190110827</v>
+      </c>
+      <c r="B396" t="n">
+        <v>2.70805020110221</v>
+      </c>
+      <c r="C396" t="n">
+        <v>0.4854166666666666</v>
+      </c>
+      <c r="D396" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="n">
+        <v>0.0008525149190110827</v>
+      </c>
+      <c r="B397" t="n">
+        <v>2.70805020110221</v>
+      </c>
+      <c r="C397" t="n">
+        <v>0.5083333333333333</v>
+      </c>
+      <c r="D397" t="n">
+        <v>0.9975706675693212</v>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="n">
+        <v>0.0008525149190110827</v>
+      </c>
+      <c r="B398" t="n">
+        <v>2.70805020110221</v>
+      </c>
+      <c r="C398" t="n">
+        <v>0.53125</v>
+      </c>
+      <c r="D398" t="n">
+        <v>0.9977252788282929</v>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="n">
+        <v>0.0008525149190110827</v>
+      </c>
+      <c r="B399" t="n">
+        <v>2.70805020110221</v>
+      </c>
+      <c r="C399" t="n">
+        <v>0.5541666666666667</v>
+      </c>
+      <c r="D399" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="n">
+        <v>0.0008525149190110827</v>
+      </c>
+      <c r="B400" t="n">
+        <v>2.70805020110221</v>
+      </c>
+      <c r="C400" t="n">
+        <v>0.5770833333333334</v>
+      </c>
+      <c r="D400" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="n">
+        <v>0.0008525149190110827</v>
+      </c>
+      <c r="B401" t="n">
+        <v>2.70805020110221</v>
+      </c>
+      <c r="C401" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D401" t="n">
+        <v>0.9972221722733274</v>
       </c>
     </row>
   </sheetData>
